--- a/stores_base.xlsx
+++ b/stores_base.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$E$1445</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4340" uniqueCount="1481">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4337" uniqueCount="1480">
   <si>
     <t>门店名称</t>
   </si>
@@ -3335,9 +3335,6 @@
   </si>
   <si>
     <t>重庆印象城蔓味轻食轻选站（闭店）</t>
-  </si>
-  <si>
-    <t>重庆龙湖时代蔓味轻食轻选站（闭店）</t>
   </si>
   <si>
     <t>抚州恒安东路林记轻选站</t>
@@ -5472,9 +5469,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E1446"/>
+  <dimension ref="A1:E1445"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="4"/>
   <cols>
+    <col min="1" max="1" width="41.5044247787611" customWidth="1"/>
     <col min="4" max="4" width="11.6637168141593"/>
     <col min="5" max="5" width="10.5309734513274"/>
   </cols>
@@ -23609,13 +23607,13 @@
         <v>6</v>
       </c>
       <c r="C1067" s="2" t="s">
-        <v>11</v>
+        <v>297</v>
       </c>
       <c r="D1067" s="2">
-        <v>106.51287</v>
+        <v>116.618881</v>
       </c>
       <c r="E1067" s="2">
-        <v>29.53435</v>
+        <v>28.230232</v>
       </c>
     </row>
     <row r="1068" spans="1:5">
@@ -23629,10 +23627,10 @@
         <v>297</v>
       </c>
       <c r="D1068" s="2">
-        <v>116.618881</v>
+        <v>116.347622</v>
       </c>
       <c r="E1068" s="2">
-        <v>28.230232</v>
+        <v>27.983852</v>
       </c>
     </row>
     <row r="1069" spans="1:5">
@@ -23646,10 +23644,10 @@
         <v>297</v>
       </c>
       <c r="D1069" s="2">
-        <v>116.347622</v>
+        <v>116.366056</v>
       </c>
       <c r="E1069" s="2">
-        <v>27.983852</v>
+        <v>27.976177</v>
       </c>
     </row>
     <row r="1070" spans="1:5">
@@ -23663,10 +23661,10 @@
         <v>297</v>
       </c>
       <c r="D1070" s="2">
-        <v>116.366056</v>
+        <v>116.357898</v>
       </c>
       <c r="E1070" s="2">
-        <v>27.976177</v>
+        <v>27.996378</v>
       </c>
     </row>
     <row r="1071" spans="1:5">
@@ -23680,10 +23678,10 @@
         <v>297</v>
       </c>
       <c r="D1071" s="2">
-        <v>116.357898</v>
+        <v>116.370926</v>
       </c>
       <c r="E1071" s="2">
-        <v>27.996378</v>
+        <v>27.997523</v>
       </c>
     </row>
     <row r="1072" spans="1:5">
@@ -23697,10 +23695,10 @@
         <v>297</v>
       </c>
       <c r="D1072" s="2">
-        <v>116.370926</v>
+        <v>116.30056</v>
       </c>
       <c r="E1072" s="2">
-        <v>27.997523</v>
+        <v>27.93593</v>
       </c>
     </row>
     <row r="1073" spans="1:5">
@@ -23714,10 +23712,10 @@
         <v>297</v>
       </c>
       <c r="D1073" s="2">
-        <v>116.30056</v>
+        <v>116.34669</v>
       </c>
       <c r="E1073" s="2">
-        <v>27.93593</v>
+        <v>27.956907</v>
       </c>
     </row>
     <row r="1074" spans="1:5">
@@ -23728,13 +23726,13 @@
         <v>6</v>
       </c>
       <c r="C1074" s="2" t="s">
-        <v>297</v>
+        <v>35</v>
       </c>
       <c r="D1074" s="2">
-        <v>116.34669</v>
+        <v>119.363362</v>
       </c>
       <c r="E1074" s="2">
-        <v>27.956907</v>
+        <v>25.726588</v>
       </c>
     </row>
     <row r="1075" spans="1:5">
@@ -23748,10 +23746,10 @@
         <v>35</v>
       </c>
       <c r="D1075" s="2">
-        <v>119.363362</v>
+        <v>119.351945</v>
       </c>
       <c r="E1075" s="2">
-        <v>25.726588</v>
+        <v>25.713781</v>
       </c>
     </row>
     <row r="1076" spans="1:5">
@@ -23765,10 +23763,10 @@
         <v>35</v>
       </c>
       <c r="D1076" s="2">
-        <v>119.351945</v>
+        <v>119.367031</v>
       </c>
       <c r="E1076" s="2">
-        <v>25.713781</v>
+        <v>25.718471</v>
       </c>
     </row>
     <row r="1077" spans="1:5">
@@ -23779,13 +23777,13 @@
         <v>6</v>
       </c>
       <c r="C1077" s="2" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="D1077" s="2">
-        <v>119.367031</v>
+        <v>123.23929</v>
       </c>
       <c r="E1077" s="2">
-        <v>25.718471</v>
+        <v>41.740754</v>
       </c>
     </row>
     <row r="1078" spans="1:5">
@@ -23796,13 +23794,13 @@
         <v>6</v>
       </c>
       <c r="C1078" s="2" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D1078" s="2">
-        <v>123.23929</v>
+        <v>118.305751</v>
       </c>
       <c r="E1078" s="2">
-        <v>41.740754</v>
+        <v>27.024627</v>
       </c>
     </row>
     <row r="1079" spans="1:5">
@@ -23816,10 +23814,10 @@
         <v>35</v>
       </c>
       <c r="D1079" s="2">
-        <v>118.305751</v>
+        <v>119.350835</v>
       </c>
       <c r="E1079" s="2">
-        <v>27.024627</v>
+        <v>25.714732</v>
       </c>
     </row>
     <row r="1080" spans="1:5">
@@ -23830,13 +23828,13 @@
         <v>6</v>
       </c>
       <c r="C1080" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D1080" s="2">
-        <v>119.350835</v>
+        <v>116.509803</v>
       </c>
       <c r="E1080" s="2">
-        <v>25.714732</v>
+        <v>39.9111</v>
       </c>
     </row>
     <row r="1081" spans="1:5">
@@ -23847,13 +23845,13 @@
         <v>6</v>
       </c>
       <c r="C1081" s="2" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D1081" s="2">
-        <v>116.509803</v>
+        <v>108.703343</v>
       </c>
       <c r="E1081" s="2">
-        <v>39.9111</v>
+        <v>34.332899</v>
       </c>
     </row>
     <row r="1082" spans="1:5">
@@ -23867,10 +23865,10 @@
         <v>13</v>
       </c>
       <c r="D1082" s="2">
-        <v>108.703343</v>
+        <v>108.896551</v>
       </c>
       <c r="E1082" s="2">
-        <v>34.332899</v>
+        <v>34.24458</v>
       </c>
     </row>
     <row r="1083" spans="1:5">
@@ -23881,13 +23879,13 @@
         <v>6</v>
       </c>
       <c r="C1083" s="2" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D1083" s="2">
-        <v>108.896551</v>
+        <v>119.35073</v>
       </c>
       <c r="E1083" s="2">
-        <v>34.24458</v>
+        <v>25.71506</v>
       </c>
     </row>
     <row r="1084" spans="1:5">
@@ -23901,10 +23899,10 @@
         <v>35</v>
       </c>
       <c r="D1084" s="2">
-        <v>119.35073</v>
+        <v>119.79874</v>
       </c>
       <c r="E1084" s="2">
-        <v>25.71506</v>
+        <v>25.50404</v>
       </c>
     </row>
     <row r="1085" spans="1:5">
@@ -23912,16 +23910,16 @@
         <v>1118</v>
       </c>
       <c r="B1085" s="2" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1085" s="2" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="D1085" s="2">
-        <v>119.79874</v>
+        <v>116.470742</v>
       </c>
       <c r="E1085" s="2">
-        <v>25.50404</v>
+        <v>39.860324</v>
       </c>
     </row>
     <row r="1086" spans="1:5">
@@ -23929,16 +23927,16 @@
         <v>1119</v>
       </c>
       <c r="B1086" s="2" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1086" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D1086" s="2">
-        <v>116.470742</v>
+        <v>119.318785</v>
       </c>
       <c r="E1086" s="2">
-        <v>39.860324</v>
+        <v>25.450867</v>
       </c>
     </row>
     <row r="1087" spans="1:5">
@@ -23952,10 +23950,10 @@
         <v>35</v>
       </c>
       <c r="D1087" s="2">
-        <v>119.318785</v>
+        <v>119.318411</v>
       </c>
       <c r="E1087" s="2">
-        <v>25.450867</v>
+        <v>25.452364</v>
       </c>
     </row>
     <row r="1088" spans="1:5">
@@ -23966,13 +23964,13 @@
         <v>6</v>
       </c>
       <c r="C1088" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D1088" s="2">
-        <v>119.318411</v>
+        <v>113.66596</v>
       </c>
       <c r="E1088" s="2">
-        <v>25.452364</v>
+        <v>34.75241</v>
       </c>
     </row>
     <row r="1089" spans="1:5">
@@ -23986,10 +23984,10 @@
         <v>38</v>
       </c>
       <c r="D1089" s="2">
-        <v>113.66596</v>
+        <v>113.785796</v>
       </c>
       <c r="E1089" s="2">
-        <v>34.75241</v>
+        <v>34.76326</v>
       </c>
     </row>
     <row r="1090" spans="1:5">
@@ -23997,16 +23995,16 @@
         <v>1123</v>
       </c>
       <c r="B1090" s="2" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1090" s="2" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D1090" s="2">
-        <v>113.785796</v>
+        <v>116.630093</v>
       </c>
       <c r="E1090" s="2">
-        <v>34.76326</v>
+        <v>39.930046</v>
       </c>
     </row>
     <row r="1091" spans="1:5">
@@ -24020,10 +24018,10 @@
         <v>45</v>
       </c>
       <c r="D1091" s="2">
-        <v>116.630093</v>
+        <v>116.332139</v>
       </c>
       <c r="E1091" s="2">
-        <v>39.930046</v>
+        <v>39.976913</v>
       </c>
     </row>
     <row r="1092" spans="1:5">
@@ -24031,16 +24029,16 @@
         <v>1125</v>
       </c>
       <c r="B1092" s="2" t="s">
-        <v>74</v>
+        <v>157</v>
       </c>
       <c r="C1092" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D1092" s="2">
-        <v>116.332139</v>
+        <v>116.509803</v>
       </c>
       <c r="E1092" s="2">
-        <v>39.976913</v>
+        <v>39.9111</v>
       </c>
     </row>
     <row r="1093" spans="1:5">
@@ -24048,16 +24046,16 @@
         <v>1126</v>
       </c>
       <c r="B1093" s="2" t="s">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="C1093" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D1093" s="2">
-        <v>116.509803</v>
+        <v>116.405683</v>
       </c>
       <c r="E1093" s="2">
-        <v>39.9111</v>
+        <v>39.951746</v>
       </c>
     </row>
     <row r="1094" spans="1:5">
@@ -24065,16 +24063,16 @@
         <v>1127</v>
       </c>
       <c r="B1094" s="2" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1094" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D1094" s="2">
-        <v>116.405683</v>
+        <v>119.373391</v>
       </c>
       <c r="E1094" s="2">
-        <v>39.951746</v>
+        <v>25.735663</v>
       </c>
     </row>
     <row r="1095" spans="1:5">
@@ -24085,13 +24083,13 @@
         <v>6</v>
       </c>
       <c r="C1095" s="2" t="s">
-        <v>35</v>
+        <v>145</v>
       </c>
       <c r="D1095" s="2">
-        <v>119.373391</v>
+        <v>121.42966</v>
       </c>
       <c r="E1095" s="2">
-        <v>25.735663</v>
+        <v>31.20433</v>
       </c>
     </row>
     <row r="1096" spans="1:5">
@@ -24102,13 +24100,13 @@
         <v>6</v>
       </c>
       <c r="C1096" s="2" t="s">
-        <v>145</v>
+        <v>225</v>
       </c>
       <c r="D1096" s="2">
-        <v>121.42966</v>
+        <v>111.50297</v>
       </c>
       <c r="E1096" s="2">
-        <v>31.20433</v>
+        <v>36.080597</v>
       </c>
     </row>
     <row r="1097" spans="1:5">
@@ -24116,16 +24114,16 @@
         <v>1130</v>
       </c>
       <c r="B1097" s="2" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1097" s="2" t="s">
-        <v>225</v>
+        <v>7</v>
       </c>
       <c r="D1097" s="2">
-        <v>111.50297</v>
+        <v>104.097664</v>
       </c>
       <c r="E1097" s="2">
-        <v>36.080597</v>
+        <v>30.55071</v>
       </c>
     </row>
     <row r="1098" spans="1:5">
@@ -24139,10 +24137,10 @@
         <v>7</v>
       </c>
       <c r="D1098" s="2">
-        <v>104.097664</v>
+        <v>103.963083</v>
       </c>
       <c r="E1098" s="2">
-        <v>30.55071</v>
+        <v>30.654582</v>
       </c>
     </row>
     <row r="1099" spans="1:5">
@@ -24150,16 +24148,16 @@
         <v>1132</v>
       </c>
       <c r="B1099" s="2" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1099" s="2" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D1099" s="2">
-        <v>103.963083</v>
+        <v>119.362204</v>
       </c>
       <c r="E1099" s="2">
-        <v>30.654582</v>
+        <v>25.756486</v>
       </c>
     </row>
     <row r="1100" spans="1:5">
@@ -24173,10 +24171,10 @@
         <v>35</v>
       </c>
       <c r="D1100" s="2">
-        <v>119.362204</v>
+        <v>119.382615</v>
       </c>
       <c r="E1100" s="2">
-        <v>25.756486</v>
+        <v>25.70125</v>
       </c>
     </row>
     <row r="1101" spans="1:5">
@@ -24187,13 +24185,13 @@
         <v>6</v>
       </c>
       <c r="C1101" s="2" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D1101" s="2">
-        <v>119.382615</v>
+        <v>114.24695</v>
       </c>
       <c r="E1101" s="2">
-        <v>25.70125</v>
+        <v>30.618919</v>
       </c>
     </row>
     <row r="1102" spans="1:5">
@@ -24207,10 +24205,10 @@
         <v>22</v>
       </c>
       <c r="D1102" s="2">
-        <v>114.24695</v>
+        <v>114.311909</v>
       </c>
       <c r="E1102" s="2">
-        <v>30.618919</v>
+        <v>30.638004</v>
       </c>
     </row>
     <row r="1103" spans="1:5">
@@ -24221,13 +24219,13 @@
         <v>6</v>
       </c>
       <c r="C1103" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D1103" s="2">
-        <v>114.311909</v>
+        <v>119.337574</v>
       </c>
       <c r="E1103" s="2">
-        <v>30.638004</v>
+        <v>25.702348</v>
       </c>
     </row>
     <row r="1104" spans="1:5">
@@ -24241,10 +24239,10 @@
         <v>35</v>
       </c>
       <c r="D1104" s="2">
-        <v>119.337574</v>
+        <v>119.592408</v>
       </c>
       <c r="E1104" s="2">
-        <v>25.702348</v>
+        <v>25.871746</v>
       </c>
     </row>
     <row r="1105" spans="1:5">
@@ -24258,10 +24256,10 @@
         <v>35</v>
       </c>
       <c r="D1105" s="2">
-        <v>119.592408</v>
+        <v>119.596655</v>
       </c>
       <c r="E1105" s="2">
-        <v>25.871746</v>
+        <v>25.876001</v>
       </c>
     </row>
     <row r="1106" spans="1:5">
@@ -24272,13 +24270,13 @@
         <v>6</v>
       </c>
       <c r="C1106" s="2" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="D1106" s="2">
-        <v>119.596655</v>
+        <v>120.397033</v>
       </c>
       <c r="E1106" s="2">
-        <v>25.876001</v>
+        <v>36.113262</v>
       </c>
     </row>
     <row r="1107" spans="1:5">
@@ -24289,13 +24287,13 @@
         <v>6</v>
       </c>
       <c r="C1107" s="2" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="D1107" s="2">
-        <v>120.397033</v>
+        <v>119.669748</v>
       </c>
       <c r="E1107" s="2">
-        <v>36.113262</v>
+        <v>25.93134</v>
       </c>
     </row>
     <row r="1108" spans="1:5">
@@ -24306,13 +24304,13 @@
         <v>6</v>
       </c>
       <c r="C1108" s="2" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D1108" s="2">
-        <v>119.669748</v>
+        <v>114.880104</v>
       </c>
       <c r="E1108" s="2">
-        <v>25.93134</v>
+        <v>30.434354</v>
       </c>
     </row>
     <row r="1109" spans="1:5">
@@ -24323,13 +24321,13 @@
         <v>6</v>
       </c>
       <c r="C1109" s="2" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D1109" s="2">
-        <v>114.880104</v>
+        <v>117.123671</v>
       </c>
       <c r="E1109" s="2">
-        <v>30.434354</v>
+        <v>40.144463</v>
       </c>
     </row>
     <row r="1110" spans="1:5">
@@ -24340,13 +24338,13 @@
         <v>6</v>
       </c>
       <c r="C1110" s="2" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D1110" s="2">
-        <v>117.123671</v>
+        <v>119.321186</v>
       </c>
       <c r="E1110" s="2">
-        <v>40.144463</v>
+        <v>25.456163</v>
       </c>
     </row>
     <row r="1111" spans="1:5">
@@ -24360,10 +24358,10 @@
         <v>35</v>
       </c>
       <c r="D1111" s="2">
-        <v>119.321186</v>
+        <v>119.787723</v>
       </c>
       <c r="E1111" s="2">
-        <v>25.456163</v>
+        <v>25.489614</v>
       </c>
     </row>
     <row r="1112" spans="1:5">
@@ -24377,10 +24375,10 @@
         <v>35</v>
       </c>
       <c r="D1112" s="2">
-        <v>119.787723</v>
+        <v>119.790551</v>
       </c>
       <c r="E1112" s="2">
-        <v>25.489614</v>
+        <v>25.486846</v>
       </c>
     </row>
     <row r="1113" spans="1:5">
@@ -24394,10 +24392,10 @@
         <v>35</v>
       </c>
       <c r="D1113" s="2">
-        <v>119.790551</v>
+        <v>119.789111</v>
       </c>
       <c r="E1113" s="2">
-        <v>25.486846</v>
+        <v>25.502795</v>
       </c>
     </row>
     <row r="1114" spans="1:5">
@@ -24411,10 +24409,10 @@
         <v>35</v>
       </c>
       <c r="D1114" s="2">
-        <v>119.789111</v>
+        <v>119.367123</v>
       </c>
       <c r="E1114" s="2">
-        <v>25.502795</v>
+        <v>25.717228</v>
       </c>
     </row>
     <row r="1115" spans="1:5">
@@ -24428,10 +24426,10 @@
         <v>35</v>
       </c>
       <c r="D1115" s="2">
-        <v>119.367123</v>
+        <v>119.363625</v>
       </c>
       <c r="E1115" s="2">
-        <v>25.717228</v>
+        <v>25.729739</v>
       </c>
     </row>
     <row r="1116" spans="1:5">
@@ -24445,10 +24443,10 @@
         <v>35</v>
       </c>
       <c r="D1116" s="2">
-        <v>119.363625</v>
+        <v>119.3468</v>
       </c>
       <c r="E1116" s="2">
-        <v>25.729739</v>
+        <v>25.715238</v>
       </c>
     </row>
     <row r="1117" spans="1:5">
@@ -24462,10 +24460,10 @@
         <v>35</v>
       </c>
       <c r="D1117" s="2">
-        <v>119.3468</v>
+        <v>119.355367</v>
       </c>
       <c r="E1117" s="2">
-        <v>25.715238</v>
+        <v>25.717866</v>
       </c>
     </row>
     <row r="1118" spans="1:5">
@@ -24479,10 +24477,10 @@
         <v>35</v>
       </c>
       <c r="D1118" s="2">
-        <v>119.355367</v>
+        <v>119.79129</v>
       </c>
       <c r="E1118" s="2">
-        <v>25.717866</v>
+        <v>25.488687</v>
       </c>
     </row>
     <row r="1119" spans="1:5">
@@ -24496,10 +24494,10 @@
         <v>35</v>
       </c>
       <c r="D1119" s="2">
-        <v>119.79129</v>
+        <v>119.799853</v>
       </c>
       <c r="E1119" s="2">
-        <v>25.488687</v>
+        <v>25.503013</v>
       </c>
     </row>
     <row r="1120" spans="1:5">
@@ -24513,10 +24511,10 @@
         <v>35</v>
       </c>
       <c r="D1120" s="2">
-        <v>119.799853</v>
+        <v>119.802143</v>
       </c>
       <c r="E1120" s="2">
-        <v>25.503013</v>
+        <v>25.50159</v>
       </c>
     </row>
     <row r="1121" spans="1:5">
@@ -24530,10 +24528,10 @@
         <v>35</v>
       </c>
       <c r="D1121" s="2">
-        <v>119.802143</v>
+        <v>119.798116</v>
       </c>
       <c r="E1121" s="2">
-        <v>25.50159</v>
+        <v>25.49188</v>
       </c>
     </row>
     <row r="1122" spans="1:5">
@@ -24547,10 +24545,10 @@
         <v>35</v>
       </c>
       <c r="D1122" s="2">
-        <v>119.798116</v>
+        <v>119.304837</v>
       </c>
       <c r="E1122" s="2">
-        <v>25.49188</v>
+        <v>25.595006</v>
       </c>
     </row>
     <row r="1123" spans="1:5">
@@ -24564,10 +24562,10 @@
         <v>35</v>
       </c>
       <c r="D1123" s="2">
-        <v>119.304837</v>
+        <v>119.788818</v>
       </c>
       <c r="E1123" s="2">
-        <v>25.595006</v>
+        <v>25.500283</v>
       </c>
     </row>
     <row r="1124" spans="1:5">
@@ -24578,13 +24576,13 @@
         <v>6</v>
       </c>
       <c r="C1124" s="2" t="s">
-        <v>35</v>
+        <v>91</v>
       </c>
       <c r="D1124" s="2">
-        <v>119.788818</v>
+        <v>123.905915</v>
       </c>
       <c r="E1124" s="2">
-        <v>25.500283</v>
+        <v>41.862292</v>
       </c>
     </row>
     <row r="1125" spans="1:5">
@@ -24595,13 +24593,13 @@
         <v>6</v>
       </c>
       <c r="C1125" s="2" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D1125" s="2">
-        <v>123.905915</v>
+        <v>119.336354</v>
       </c>
       <c r="E1125" s="2">
-        <v>41.862292</v>
+        <v>25.714245</v>
       </c>
     </row>
     <row r="1126" spans="1:5">
@@ -24615,10 +24613,10 @@
         <v>35</v>
       </c>
       <c r="D1126" s="2">
-        <v>119.336354</v>
+        <v>119.796666</v>
       </c>
       <c r="E1126" s="2">
-        <v>25.714245</v>
+        <v>25.482054</v>
       </c>
     </row>
     <row r="1127" spans="1:5">
@@ -24629,13 +24627,13 @@
         <v>6</v>
       </c>
       <c r="C1127" s="2" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="D1127" s="2">
-        <v>119.796666</v>
+        <v>114.476729</v>
       </c>
       <c r="E1127" s="2">
-        <v>25.482054</v>
+        <v>38.030825</v>
       </c>
     </row>
     <row r="1128" spans="1:5">
@@ -24646,13 +24644,13 @@
         <v>6</v>
       </c>
       <c r="C1128" s="2" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="D1128" s="2">
-        <v>114.476729</v>
+        <v>120.397461</v>
       </c>
       <c r="E1128" s="2">
-        <v>38.030825</v>
+        <v>36.126606</v>
       </c>
     </row>
     <row r="1129" spans="1:5">
@@ -24666,10 +24664,10 @@
         <v>78</v>
       </c>
       <c r="D1129" s="2">
-        <v>120.397461</v>
+        <v>120.372561</v>
       </c>
       <c r="E1129" s="2">
-        <v>36.126606</v>
+        <v>36.098061</v>
       </c>
     </row>
     <row r="1130" spans="1:5">
@@ -24677,16 +24675,16 @@
         <v>1163</v>
       </c>
       <c r="B1130" s="2" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1130" s="2" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="D1130" s="2">
-        <v>120.372561</v>
+        <v>116.328274</v>
       </c>
       <c r="E1130" s="2">
-        <v>36.098061</v>
+        <v>40.010144</v>
       </c>
     </row>
     <row r="1131" spans="1:5">
@@ -24694,16 +24692,16 @@
         <v>1164</v>
       </c>
       <c r="B1131" s="2" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1131" s="2" t="s">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="D1131" s="2">
-        <v>116.328274</v>
+        <v>114.280869</v>
       </c>
       <c r="E1131" s="2">
-        <v>40.010144</v>
+        <v>30.670739</v>
       </c>
     </row>
     <row r="1132" spans="1:5">
@@ -24714,13 +24712,13 @@
         <v>6</v>
       </c>
       <c r="C1132" s="2" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="D1132" s="2">
-        <v>114.280869</v>
+        <v>119.324194</v>
       </c>
       <c r="E1132" s="2">
-        <v>30.670739</v>
+        <v>26.137441</v>
       </c>
     </row>
     <row r="1133" spans="1:5">
@@ -24734,10 +24732,10 @@
         <v>35</v>
       </c>
       <c r="D1133" s="2">
-        <v>119.324194</v>
+        <v>119.32569</v>
       </c>
       <c r="E1133" s="2">
-        <v>26.137441</v>
+        <v>25.726334</v>
       </c>
     </row>
     <row r="1134" spans="1:5">
@@ -24745,16 +24743,16 @@
         <v>1167</v>
       </c>
       <c r="B1134" s="2" t="s">
-        <v>6</v>
+        <v>157</v>
       </c>
       <c r="C1134" s="2" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="D1134" s="2">
-        <v>119.32569</v>
+        <v>106.516129</v>
       </c>
       <c r="E1134" s="2">
-        <v>25.726334</v>
+        <v>29.54967</v>
       </c>
     </row>
     <row r="1135" spans="1:5">
@@ -24762,33 +24760,33 @@
         <v>1168</v>
       </c>
       <c r="B1135" s="2" t="s">
-        <v>157</v>
+        <v>6</v>
       </c>
       <c r="C1135" s="2" t="s">
-        <v>11</v>
+        <v>1169</v>
       </c>
       <c r="D1135" s="2">
-        <v>106.516129</v>
+        <v>114.215306</v>
       </c>
       <c r="E1135" s="2">
-        <v>29.54967</v>
+        <v>22.321525</v>
       </c>
     </row>
     <row r="1136" spans="1:5">
       <c r="A1136" s="2" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B1136" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1136" s="2" t="s">
         <v>1169</v>
       </c>
-      <c r="B1136" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1136" s="2" t="s">
-        <v>1170</v>
-      </c>
       <c r="D1136" s="2">
-        <v>114.215306</v>
+        <v>114.171203</v>
       </c>
       <c r="E1136" s="2">
-        <v>22.321525</v>
+        <v>22.277468</v>
       </c>
     </row>
     <row r="1137" spans="1:5">
@@ -24799,13 +24797,13 @@
         <v>6</v>
       </c>
       <c r="C1137" s="2" t="s">
-        <v>1170</v>
+        <v>45</v>
       </c>
       <c r="D1137" s="2">
-        <v>114.171203</v>
+        <v>116.309853</v>
       </c>
       <c r="E1137" s="2">
-        <v>22.277468</v>
+        <v>40.043295</v>
       </c>
     </row>
     <row r="1138" spans="1:5">
@@ -24819,10 +24817,10 @@
         <v>45</v>
       </c>
       <c r="D1138" s="2">
-        <v>116.309853</v>
+        <v>116.308681</v>
       </c>
       <c r="E1138" s="2">
-        <v>40.043295</v>
+        <v>40.0374</v>
       </c>
     </row>
     <row r="1139" spans="1:5">
@@ -24833,13 +24831,13 @@
         <v>6</v>
       </c>
       <c r="C1139" s="2" t="s">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="D1139" s="2">
-        <v>116.308681</v>
+        <v>112.529773</v>
       </c>
       <c r="E1139" s="2">
-        <v>40.0374</v>
+        <v>37.832004</v>
       </c>
     </row>
     <row r="1140" spans="1:5">
@@ -24850,13 +24848,13 @@
         <v>6</v>
       </c>
       <c r="C1140" s="2" t="s">
-        <v>225</v>
+        <v>297</v>
       </c>
       <c r="D1140" s="2">
-        <v>112.529773</v>
+        <v>114.880783</v>
       </c>
       <c r="E1140" s="2">
-        <v>37.832004</v>
+        <v>25.880303</v>
       </c>
     </row>
     <row r="1141" spans="1:5">
@@ -24864,16 +24862,16 @@
         <v>1175</v>
       </c>
       <c r="B1141" s="2" t="s">
-        <v>6</v>
+        <v>157</v>
       </c>
       <c r="C1141" s="2" t="s">
-        <v>297</v>
+        <v>141</v>
       </c>
       <c r="D1141" s="2">
-        <v>114.880783</v>
+        <v>118.088934</v>
       </c>
       <c r="E1141" s="2">
-        <v>25.880303</v>
+        <v>39.575529</v>
       </c>
     </row>
     <row r="1142" spans="1:5">
@@ -24881,16 +24879,16 @@
         <v>1176</v>
       </c>
       <c r="B1142" s="2" t="s">
-        <v>157</v>
+        <v>6</v>
       </c>
       <c r="C1142" s="2" t="s">
-        <v>141</v>
+        <v>97</v>
       </c>
       <c r="D1142" s="2">
-        <v>118.088934</v>
+        <v>119.616946</v>
       </c>
       <c r="E1142" s="2">
-        <v>39.575529</v>
+        <v>32.399369</v>
       </c>
     </row>
     <row r="1143" spans="1:5">
@@ -24901,13 +24899,13 @@
         <v>6</v>
       </c>
       <c r="C1143" s="2" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D1143" s="2">
-        <v>119.616946</v>
+        <v>120.31517</v>
       </c>
       <c r="E1143" s="2">
-        <v>32.399369</v>
+        <v>36.06441</v>
       </c>
     </row>
     <row r="1144" spans="1:5">
@@ -24921,10 +24919,10 @@
         <v>78</v>
       </c>
       <c r="D1144" s="2">
-        <v>120.31517</v>
+        <v>120.40108</v>
       </c>
       <c r="E1144" s="2">
-        <v>36.06441</v>
+        <v>36.06209</v>
       </c>
     </row>
     <row r="1145" spans="1:5">
@@ -24938,10 +24936,10 @@
         <v>78</v>
       </c>
       <c r="D1145" s="2">
-        <v>120.40108</v>
+        <v>120.154749</v>
       </c>
       <c r="E1145" s="2">
-        <v>36.06209</v>
+        <v>35.982798</v>
       </c>
     </row>
     <row r="1146" spans="1:5">
@@ -24955,10 +24953,10 @@
         <v>78</v>
       </c>
       <c r="D1146" s="2">
-        <v>120.154749</v>
+        <v>120.374069</v>
       </c>
       <c r="E1146" s="2">
-        <v>35.982798</v>
+        <v>36.083067</v>
       </c>
     </row>
     <row r="1147" spans="1:5">
@@ -24969,13 +24967,13 @@
         <v>6</v>
       </c>
       <c r="C1147" s="2" t="s">
-        <v>78</v>
+        <v>22</v>
       </c>
       <c r="D1147" s="2">
-        <v>120.374069</v>
+        <v>114.264953</v>
       </c>
       <c r="E1147" s="2">
-        <v>36.083067</v>
+        <v>30.567515</v>
       </c>
     </row>
     <row r="1148" spans="1:5">
@@ -24986,13 +24984,13 @@
         <v>6</v>
       </c>
       <c r="C1148" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D1148" s="2">
-        <v>114.264953</v>
+        <v>108.926141</v>
       </c>
       <c r="E1148" s="2">
-        <v>30.567515</v>
+        <v>34.330208</v>
       </c>
     </row>
     <row r="1149" spans="1:5">
@@ -25003,13 +25001,13 @@
         <v>6</v>
       </c>
       <c r="C1149" s="2" t="s">
-        <v>13</v>
+        <v>78</v>
       </c>
       <c r="D1149" s="2">
-        <v>108.926141</v>
+        <v>120.441607</v>
       </c>
       <c r="E1149" s="2">
-        <v>34.330208</v>
+        <v>36.161067</v>
       </c>
     </row>
     <row r="1150" spans="1:5">
@@ -25023,10 +25021,10 @@
         <v>78</v>
       </c>
       <c r="D1150" s="2">
-        <v>120.441607</v>
+        <v>120.477855</v>
       </c>
       <c r="E1150" s="2">
-        <v>36.161067</v>
+        <v>36.182806</v>
       </c>
     </row>
     <row r="1151" spans="1:5">
@@ -25040,10 +25038,10 @@
         <v>78</v>
       </c>
       <c r="D1151" s="2">
-        <v>120.477855</v>
+        <v>120.476852</v>
       </c>
       <c r="E1151" s="2">
-        <v>36.182806</v>
+        <v>36.179569</v>
       </c>
     </row>
     <row r="1152" spans="1:5">
@@ -25057,10 +25055,10 @@
         <v>78</v>
       </c>
       <c r="D1152" s="2">
-        <v>120.476852</v>
+        <v>120.468682</v>
       </c>
       <c r="E1152" s="2">
-        <v>36.179569</v>
+        <v>36.170977</v>
       </c>
     </row>
     <row r="1153" spans="1:5">
@@ -25074,10 +25072,10 @@
         <v>78</v>
       </c>
       <c r="D1153" s="2">
-        <v>120.468682</v>
+        <v>120.44845</v>
       </c>
       <c r="E1153" s="2">
-        <v>36.170977</v>
+        <v>36.165534</v>
       </c>
     </row>
     <row r="1154" spans="1:5">
@@ -25091,10 +25089,10 @@
         <v>78</v>
       </c>
       <c r="D1154" s="2">
-        <v>120.44845</v>
+        <v>120.425188</v>
       </c>
       <c r="E1154" s="2">
-        <v>36.165534</v>
+        <v>36.17145</v>
       </c>
     </row>
     <row r="1155" spans="1:5">
@@ -25108,10 +25106,10 @@
         <v>78</v>
       </c>
       <c r="D1155" s="2">
-        <v>120.425188</v>
+        <v>120.414281</v>
       </c>
       <c r="E1155" s="2">
-        <v>36.17145</v>
+        <v>36.17421</v>
       </c>
     </row>
     <row r="1156" spans="1:5">
@@ -25125,10 +25123,10 @@
         <v>78</v>
       </c>
       <c r="D1156" s="2">
-        <v>120.414281</v>
+        <v>120.431885</v>
       </c>
       <c r="E1156" s="2">
-        <v>36.17421</v>
+        <v>36.162243</v>
       </c>
     </row>
     <row r="1157" spans="1:5">
@@ -25142,10 +25140,10 @@
         <v>78</v>
       </c>
       <c r="D1157" s="2">
-        <v>120.431885</v>
+        <v>120.429633</v>
       </c>
       <c r="E1157" s="2">
-        <v>36.162243</v>
+        <v>36.155855</v>
       </c>
     </row>
     <row r="1158" spans="1:5">
@@ -25159,10 +25157,10 @@
         <v>78</v>
       </c>
       <c r="D1158" s="2">
-        <v>120.429633</v>
+        <v>120.430573</v>
       </c>
       <c r="E1158" s="2">
-        <v>36.155855</v>
+        <v>36.189453</v>
       </c>
     </row>
     <row r="1159" spans="1:5">
@@ -25176,10 +25174,10 @@
         <v>78</v>
       </c>
       <c r="D1159" s="2">
-        <v>120.430573</v>
+        <v>120.425964</v>
       </c>
       <c r="E1159" s="2">
-        <v>36.189453</v>
+        <v>36.185931</v>
       </c>
     </row>
     <row r="1160" spans="1:5">
@@ -25193,10 +25191,10 @@
         <v>78</v>
       </c>
       <c r="D1160" s="2">
-        <v>120.425964</v>
+        <v>120.419745</v>
       </c>
       <c r="E1160" s="2">
-        <v>36.185931</v>
+        <v>36.154068</v>
       </c>
     </row>
     <row r="1161" spans="1:5">
@@ -25210,10 +25208,10 @@
         <v>78</v>
       </c>
       <c r="D1161" s="2">
-        <v>120.419745</v>
+        <v>120.425079</v>
       </c>
       <c r="E1161" s="2">
-        <v>36.154068</v>
+        <v>36.153944</v>
       </c>
     </row>
     <row r="1162" spans="1:5">
@@ -25227,10 +25225,10 @@
         <v>78</v>
       </c>
       <c r="D1162" s="2">
-        <v>120.425079</v>
+        <v>120.42797</v>
       </c>
       <c r="E1162" s="2">
-        <v>36.153944</v>
+        <v>36.1494</v>
       </c>
     </row>
     <row r="1163" spans="1:5">
@@ -25244,10 +25242,10 @@
         <v>78</v>
       </c>
       <c r="D1163" s="2">
-        <v>120.42797</v>
+        <v>120.427264</v>
       </c>
       <c r="E1163" s="2">
-        <v>36.1494</v>
+        <v>36.146161</v>
       </c>
     </row>
     <row r="1164" spans="1:5">
@@ -25261,10 +25259,10 @@
         <v>78</v>
       </c>
       <c r="D1164" s="2">
-        <v>120.427264</v>
+        <v>120.427705</v>
       </c>
       <c r="E1164" s="2">
-        <v>36.146161</v>
+        <v>36.1431</v>
       </c>
     </row>
     <row r="1165" spans="1:5">
@@ -25278,10 +25276,10 @@
         <v>78</v>
       </c>
       <c r="D1165" s="2">
-        <v>120.427705</v>
+        <v>120.421864</v>
       </c>
       <c r="E1165" s="2">
-        <v>36.1431</v>
+        <v>36.138303</v>
       </c>
     </row>
     <row r="1166" spans="1:5">
@@ -25295,10 +25293,10 @@
         <v>78</v>
       </c>
       <c r="D1166" s="2">
-        <v>120.421864</v>
+        <v>120.42085</v>
       </c>
       <c r="E1166" s="2">
-        <v>36.138303</v>
+        <v>36.122428</v>
       </c>
     </row>
     <row r="1167" spans="1:5">
@@ -25312,10 +25310,10 @@
         <v>78</v>
       </c>
       <c r="D1167" s="2">
-        <v>120.42085</v>
+        <v>120.430771</v>
       </c>
       <c r="E1167" s="2">
-        <v>36.122428</v>
+        <v>36.116352</v>
       </c>
     </row>
     <row r="1168" spans="1:5">
@@ -25329,10 +25327,10 @@
         <v>78</v>
       </c>
       <c r="D1168" s="2">
-        <v>120.430771</v>
+        <v>120.433759</v>
       </c>
       <c r="E1168" s="2">
-        <v>36.116352</v>
+        <v>36.105141</v>
       </c>
     </row>
     <row r="1169" spans="1:5">
@@ -25346,10 +25344,10 @@
         <v>78</v>
       </c>
       <c r="D1169" s="2">
-        <v>120.433759</v>
+        <v>120.411947</v>
       </c>
       <c r="E1169" s="2">
-        <v>36.105141</v>
+        <v>36.117325</v>
       </c>
     </row>
     <row r="1170" spans="1:5">
@@ -25363,10 +25361,10 @@
         <v>78</v>
       </c>
       <c r="D1170" s="2">
-        <v>120.411947</v>
+        <v>116.956736</v>
       </c>
       <c r="E1170" s="2">
-        <v>36.117325</v>
+        <v>36.663854</v>
       </c>
     </row>
     <row r="1171" spans="1:5">
@@ -25380,10 +25378,10 @@
         <v>78</v>
       </c>
       <c r="D1171" s="2">
-        <v>116.956736</v>
+        <v>116.973663</v>
       </c>
       <c r="E1171" s="2">
-        <v>36.663854</v>
+        <v>36.589183</v>
       </c>
     </row>
     <row r="1172" spans="1:5">
@@ -25397,10 +25395,10 @@
         <v>78</v>
       </c>
       <c r="D1172" s="2">
-        <v>116.973663</v>
+        <v>117.031769</v>
       </c>
       <c r="E1172" s="2">
-        <v>36.589183</v>
+        <v>36.665462</v>
       </c>
     </row>
     <row r="1173" spans="1:5">
@@ -25414,10 +25412,10 @@
         <v>78</v>
       </c>
       <c r="D1173" s="2">
-        <v>117.031769</v>
+        <v>116.917197</v>
       </c>
       <c r="E1173" s="2">
-        <v>36.665462</v>
+        <v>36.671701</v>
       </c>
     </row>
     <row r="1174" spans="1:5">
@@ -25431,10 +25429,10 @@
         <v>78</v>
       </c>
       <c r="D1174" s="2">
-        <v>116.917197</v>
+        <v>117.030715</v>
       </c>
       <c r="E1174" s="2">
-        <v>36.671701</v>
+        <v>36.664434</v>
       </c>
     </row>
     <row r="1175" spans="1:5">
@@ -25448,10 +25446,10 @@
         <v>78</v>
       </c>
       <c r="D1175" s="2">
-        <v>117.030715</v>
+        <v>117.045461</v>
       </c>
       <c r="E1175" s="2">
-        <v>36.664434</v>
+        <v>36.680975</v>
       </c>
     </row>
     <row r="1176" spans="1:5">
@@ -25465,10 +25463,10 @@
         <v>78</v>
       </c>
       <c r="D1176" s="2">
-        <v>117.045461</v>
+        <v>117.049135</v>
       </c>
       <c r="E1176" s="2">
-        <v>36.680975</v>
+        <v>36.672041</v>
       </c>
     </row>
     <row r="1177" spans="1:5">
@@ -25482,10 +25480,10 @@
         <v>78</v>
       </c>
       <c r="D1177" s="2">
-        <v>117.049135</v>
+        <v>117.037437</v>
       </c>
       <c r="E1177" s="2">
-        <v>36.672041</v>
+        <v>36.698831</v>
       </c>
     </row>
     <row r="1178" spans="1:5">
@@ -25499,10 +25497,10 @@
         <v>78</v>
       </c>
       <c r="D1178" s="2">
-        <v>117.037437</v>
+        <v>117.055468</v>
       </c>
       <c r="E1178" s="2">
-        <v>36.698831</v>
+        <v>36.678305</v>
       </c>
     </row>
     <row r="1179" spans="1:5">
@@ -25510,16 +25508,16 @@
         <v>1213</v>
       </c>
       <c r="B1179" s="2" t="s">
-        <v>6</v>
+        <v>157</v>
       </c>
       <c r="C1179" s="2" t="s">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="D1179" s="2">
-        <v>117.055468</v>
+        <v>106.541818</v>
       </c>
       <c r="E1179" s="2">
-        <v>36.678305</v>
+        <v>29.636115</v>
       </c>
     </row>
     <row r="1180" spans="1:5">
@@ -25527,16 +25525,16 @@
         <v>1214</v>
       </c>
       <c r="B1180" s="2" t="s">
-        <v>157</v>
+        <v>6</v>
       </c>
       <c r="C1180" s="2" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="D1180" s="2">
-        <v>106.541818</v>
+        <v>120.148032</v>
       </c>
       <c r="E1180" s="2">
-        <v>29.636115</v>
+        <v>35.986061</v>
       </c>
     </row>
     <row r="1181" spans="1:5">
@@ -25550,10 +25548,10 @@
         <v>78</v>
       </c>
       <c r="D1181" s="2">
-        <v>120.148032</v>
+        <v>120.439586</v>
       </c>
       <c r="E1181" s="2">
-        <v>35.986061</v>
+        <v>36.113685</v>
       </c>
     </row>
     <row r="1182" spans="1:5">
@@ -25567,10 +25565,10 @@
         <v>78</v>
       </c>
       <c r="D1182" s="2">
-        <v>120.439586</v>
+        <v>120.445328</v>
       </c>
       <c r="E1182" s="2">
-        <v>36.113685</v>
+        <v>36.121273</v>
       </c>
     </row>
     <row r="1183" spans="1:5">
@@ -25584,10 +25582,10 @@
         <v>78</v>
       </c>
       <c r="D1183" s="2">
-        <v>120.445328</v>
+        <v>120.456056</v>
       </c>
       <c r="E1183" s="2">
-        <v>36.121273</v>
+        <v>36.116507</v>
       </c>
     </row>
     <row r="1184" spans="1:5">
@@ -25601,10 +25599,10 @@
         <v>78</v>
       </c>
       <c r="D1184" s="2">
-        <v>120.456056</v>
+        <v>120.45235</v>
       </c>
       <c r="E1184" s="2">
-        <v>36.116507</v>
+        <v>36.10785</v>
       </c>
     </row>
     <row r="1185" spans="1:5">
@@ -25618,10 +25616,10 @@
         <v>78</v>
       </c>
       <c r="D1185" s="2">
-        <v>120.45235</v>
+        <v>120.460158</v>
       </c>
       <c r="E1185" s="2">
-        <v>36.10785</v>
+        <v>36.094956</v>
       </c>
     </row>
     <row r="1186" spans="1:5">
@@ -25635,10 +25633,10 @@
         <v>78</v>
       </c>
       <c r="D1186" s="2">
-        <v>120.460158</v>
+        <v>120.497482</v>
       </c>
       <c r="E1186" s="2">
-        <v>36.094956</v>
+        <v>36.095359</v>
       </c>
     </row>
     <row r="1187" spans="1:5">
@@ -25652,10 +25650,10 @@
         <v>78</v>
       </c>
       <c r="D1187" s="2">
-        <v>120.497482</v>
+        <v>120.397528</v>
       </c>
       <c r="E1187" s="2">
-        <v>36.095359</v>
+        <v>36.069634</v>
       </c>
     </row>
     <row r="1188" spans="1:5">
@@ -25669,10 +25667,10 @@
         <v>78</v>
       </c>
       <c r="D1188" s="2">
-        <v>120.397528</v>
+        <v>120.3979</v>
       </c>
       <c r="E1188" s="2">
-        <v>36.069634</v>
+        <v>36.07113</v>
       </c>
     </row>
     <row r="1189" spans="1:5">
@@ -25683,13 +25681,13 @@
         <v>6</v>
       </c>
       <c r="C1189" s="2" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="D1189" s="2">
-        <v>120.3979</v>
+        <v>119.380817</v>
       </c>
       <c r="E1189" s="2">
-        <v>36.07113</v>
+        <v>25.721605</v>
       </c>
     </row>
     <row r="1190" spans="1:5">
@@ -25703,10 +25701,10 @@
         <v>35</v>
       </c>
       <c r="D1190" s="2">
-        <v>119.380817</v>
+        <v>119.375331</v>
       </c>
       <c r="E1190" s="2">
-        <v>25.721605</v>
+        <v>25.718659</v>
       </c>
     </row>
     <row r="1191" spans="1:5">
@@ -25720,10 +25718,10 @@
         <v>35</v>
       </c>
       <c r="D1191" s="2">
-        <v>119.375331</v>
+        <v>119.380985</v>
       </c>
       <c r="E1191" s="2">
-        <v>25.718659</v>
+        <v>25.716524</v>
       </c>
     </row>
     <row r="1192" spans="1:5">
@@ -25737,10 +25735,10 @@
         <v>35</v>
       </c>
       <c r="D1192" s="2">
-        <v>119.380985</v>
+        <v>119.379784</v>
       </c>
       <c r="E1192" s="2">
-        <v>25.716524</v>
+        <v>25.720172</v>
       </c>
     </row>
     <row r="1193" spans="1:5">
@@ -25754,10 +25752,10 @@
         <v>35</v>
       </c>
       <c r="D1193" s="2">
-        <v>119.379784</v>
+        <v>119.362995</v>
       </c>
       <c r="E1193" s="2">
-        <v>25.720172</v>
+        <v>25.71616</v>
       </c>
     </row>
     <row r="1194" spans="1:5">
@@ -25771,10 +25769,10 @@
         <v>35</v>
       </c>
       <c r="D1194" s="2">
-        <v>119.362995</v>
+        <v>119.349369</v>
       </c>
       <c r="E1194" s="2">
-        <v>25.71616</v>
+        <v>25.715986</v>
       </c>
     </row>
     <row r="1195" spans="1:5">
@@ -25788,27 +25786,27 @@
         <v>35</v>
       </c>
       <c r="D1195" s="2">
-        <v>119.349369</v>
+        <v>119.346084</v>
       </c>
       <c r="E1195" s="2">
-        <v>25.715986</v>
+        <v>25.717384</v>
       </c>
     </row>
     <row r="1196" spans="1:5">
-      <c r="A1196" s="2" t="s">
+      <c r="A1196" t="s">
         <v>1230</v>
       </c>
-      <c r="B1196" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1196" s="2" t="s">
+      <c r="B1196" t="s">
+        <v>6</v>
+      </c>
+      <c r="C1196" t="s">
         <v>35</v>
       </c>
-      <c r="D1196" s="2">
-        <v>119.346084</v>
-      </c>
-      <c r="E1196" s="2">
-        <v>25.717384</v>
+      <c r="D1196">
+        <v>119.794567</v>
+      </c>
+      <c r="E1196">
+        <v>25.487314</v>
       </c>
     </row>
     <row r="1197" spans="1:5">
@@ -25822,10 +25820,10 @@
         <v>35</v>
       </c>
       <c r="D1197">
-        <v>119.794567</v>
+        <v>119.798468</v>
       </c>
       <c r="E1197">
-        <v>25.487314</v>
+        <v>25.505218</v>
       </c>
     </row>
     <row r="1198" spans="1:5">
@@ -25839,10 +25837,10 @@
         <v>35</v>
       </c>
       <c r="D1198">
-        <v>119.798468</v>
+        <v>119.337195</v>
       </c>
       <c r="E1198">
-        <v>25.505218</v>
+        <v>25.707855</v>
       </c>
     </row>
     <row r="1199" spans="1:5">
@@ -25856,10 +25854,10 @@
         <v>35</v>
       </c>
       <c r="D1199">
-        <v>119.337195</v>
+        <v>119.338584</v>
       </c>
       <c r="E1199">
-        <v>25.707855</v>
+        <v>25.715573</v>
       </c>
     </row>
     <row r="1200" spans="1:5">
@@ -25873,10 +25871,10 @@
         <v>35</v>
       </c>
       <c r="D1200">
-        <v>119.338584</v>
+        <v>119.779022</v>
       </c>
       <c r="E1200">
-        <v>25.715573</v>
+        <v>25.493495</v>
       </c>
     </row>
     <row r="1201" spans="1:5">
@@ -25890,10 +25888,10 @@
         <v>35</v>
       </c>
       <c r="D1201">
-        <v>119.779022</v>
+        <v>119.790548</v>
       </c>
       <c r="E1201">
-        <v>25.493495</v>
+        <v>25.490642</v>
       </c>
     </row>
     <row r="1202" spans="1:5">
@@ -25901,16 +25899,16 @@
         <v>1236</v>
       </c>
       <c r="B1202" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1202" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="D1202">
-        <v>119.790548</v>
+        <v>111.296124</v>
       </c>
       <c r="E1202">
-        <v>25.490642</v>
+        <v>30.702385</v>
       </c>
     </row>
     <row r="1203" spans="1:5">
@@ -25924,10 +25922,10 @@
         <v>22</v>
       </c>
       <c r="D1203">
-        <v>111.296124</v>
+        <v>114.205855</v>
       </c>
       <c r="E1203">
-        <v>30.702385</v>
+        <v>30.553782</v>
       </c>
     </row>
     <row r="1204" spans="1:5">
@@ -25935,16 +25933,16 @@
         <v>1238</v>
       </c>
       <c r="B1204" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1204" t="s">
-        <v>22</v>
+        <v>45</v>
       </c>
       <c r="D1204">
-        <v>114.205855</v>
+        <v>116.372804</v>
       </c>
       <c r="E1204">
-        <v>30.553782</v>
+        <v>39.953202</v>
       </c>
     </row>
     <row r="1205" spans="1:5">
@@ -25955,13 +25953,13 @@
         <v>6</v>
       </c>
       <c r="C1205" t="s">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="D1205">
-        <v>116.372804</v>
+        <v>112.529773</v>
       </c>
       <c r="E1205">
-        <v>39.953202</v>
+        <v>37.832004</v>
       </c>
     </row>
     <row r="1206" spans="1:5">
@@ -25972,13 +25970,13 @@
         <v>6</v>
       </c>
       <c r="C1206" t="s">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="D1206">
-        <v>112.529773</v>
+        <v>113.140127</v>
       </c>
       <c r="E1206">
-        <v>37.832004</v>
+        <v>23.03017</v>
       </c>
     </row>
     <row r="1207" spans="1:5">
@@ -25989,13 +25987,13 @@
         <v>6</v>
       </c>
       <c r="C1207" t="s">
-        <v>20</v>
+        <v>297</v>
       </c>
       <c r="D1207">
-        <v>113.140127</v>
+        <v>117.937039</v>
       </c>
       <c r="E1207">
-        <v>23.03017</v>
+        <v>28.449776</v>
       </c>
     </row>
     <row r="1208" spans="1:5">
@@ -26009,10 +26007,10 @@
         <v>297</v>
       </c>
       <c r="D1208">
-        <v>117.937039</v>
+        <v>117.970304</v>
       </c>
       <c r="E1208">
-        <v>28.449776</v>
+        <v>28.44322</v>
       </c>
     </row>
     <row r="1209" spans="1:5">
@@ -26026,10 +26024,10 @@
         <v>297</v>
       </c>
       <c r="D1209">
-        <v>117.970304</v>
+        <v>117.980717</v>
       </c>
       <c r="E1209">
-        <v>28.44322</v>
+        <v>28.460898</v>
       </c>
     </row>
     <row r="1210" spans="1:5">
@@ -26043,10 +26041,10 @@
         <v>297</v>
       </c>
       <c r="D1210">
-        <v>117.980717</v>
+        <v>117.92273</v>
       </c>
       <c r="E1210">
-        <v>28.460898</v>
+        <v>28.438097</v>
       </c>
     </row>
     <row r="1211" spans="1:5">
@@ -26057,13 +26055,13 @@
         <v>6</v>
       </c>
       <c r="C1211" t="s">
-        <v>297</v>
+        <v>78</v>
       </c>
       <c r="D1211">
-        <v>117.92273</v>
+        <v>117.084924</v>
       </c>
       <c r="E1211">
-        <v>28.438097</v>
+        <v>36.685353</v>
       </c>
     </row>
     <row r="1212" spans="1:5">
@@ -26077,10 +26075,10 @@
         <v>78</v>
       </c>
       <c r="D1212">
-        <v>117.084924</v>
+        <v>117.095139</v>
       </c>
       <c r="E1212">
-        <v>36.685353</v>
+        <v>36.749145</v>
       </c>
     </row>
     <row r="1213" spans="1:5">
@@ -26094,10 +26092,10 @@
         <v>78</v>
       </c>
       <c r="D1213">
-        <v>117.095139</v>
+        <v>117.120041</v>
       </c>
       <c r="E1213">
-        <v>36.749145</v>
+        <v>36.718778</v>
       </c>
     </row>
     <row r="1214" spans="1:5">
@@ -26111,10 +26109,10 @@
         <v>78</v>
       </c>
       <c r="D1214">
-        <v>117.120041</v>
+        <v>117.098477</v>
       </c>
       <c r="E1214">
-        <v>36.718778</v>
+        <v>36.674913</v>
       </c>
     </row>
     <row r="1215" spans="1:5">
@@ -26128,10 +26126,10 @@
         <v>78</v>
       </c>
       <c r="D1215">
-        <v>117.098477</v>
+        <v>120.398851</v>
       </c>
       <c r="E1215">
-        <v>36.674913</v>
+        <v>36.074547</v>
       </c>
     </row>
     <row r="1216" spans="1:5">
@@ -26145,10 +26143,10 @@
         <v>78</v>
       </c>
       <c r="D1216">
-        <v>120.398851</v>
+        <v>120.40776</v>
       </c>
       <c r="E1216">
-        <v>36.074547</v>
+        <v>36.07771</v>
       </c>
     </row>
     <row r="1217" spans="1:5">
@@ -26162,10 +26160,10 @@
         <v>78</v>
       </c>
       <c r="D1217">
-        <v>120.40776</v>
+        <v>120.404218</v>
       </c>
       <c r="E1217">
-        <v>36.07771</v>
+        <v>36.079386</v>
       </c>
     </row>
     <row r="1218" spans="1:5">
@@ -26179,10 +26177,10 @@
         <v>78</v>
       </c>
       <c r="D1218">
-        <v>120.404218</v>
+        <v>120.367191</v>
       </c>
       <c r="E1218">
-        <v>36.079386</v>
+        <v>36.087618</v>
       </c>
     </row>
     <row r="1219" spans="1:5">
@@ -26196,10 +26194,10 @@
         <v>78</v>
       </c>
       <c r="D1219">
-        <v>120.367191</v>
+        <v>120.396995</v>
       </c>
       <c r="E1219">
-        <v>36.087618</v>
+        <v>36.116741</v>
       </c>
     </row>
     <row r="1220" spans="1:5">
@@ -26213,10 +26211,10 @@
         <v>78</v>
       </c>
       <c r="D1220">
-        <v>120.396995</v>
+        <v>120.386505</v>
       </c>
       <c r="E1220">
-        <v>36.116741</v>
+        <v>36.095459</v>
       </c>
     </row>
     <row r="1221" spans="1:5">
@@ -26230,10 +26228,10 @@
         <v>78</v>
       </c>
       <c r="D1221">
-        <v>120.386505</v>
+        <v>120.376252</v>
       </c>
       <c r="E1221">
-        <v>36.095459</v>
+        <v>36.097596</v>
       </c>
     </row>
     <row r="1222" spans="1:5">
@@ -26247,10 +26245,10 @@
         <v>78</v>
       </c>
       <c r="D1222">
-        <v>120.376252</v>
+        <v>120.374357</v>
       </c>
       <c r="E1222">
-        <v>36.097596</v>
+        <v>36.099785</v>
       </c>
     </row>
     <row r="1223" spans="1:5">
@@ -26264,10 +26262,10 @@
         <v>78</v>
       </c>
       <c r="D1223">
-        <v>120.374357</v>
+        <v>120.376514</v>
       </c>
       <c r="E1223">
-        <v>36.099785</v>
+        <v>36.10251</v>
       </c>
     </row>
     <row r="1224" spans="1:5">
@@ -26281,10 +26279,10 @@
         <v>78</v>
       </c>
       <c r="D1224">
-        <v>120.376514</v>
+        <v>120.381796</v>
       </c>
       <c r="E1224">
-        <v>36.10251</v>
+        <v>36.102732</v>
       </c>
     </row>
     <row r="1225" spans="1:5">
@@ -26298,10 +26296,10 @@
         <v>78</v>
       </c>
       <c r="D1225">
-        <v>120.381796</v>
+        <v>120.39126</v>
       </c>
       <c r="E1225">
-        <v>36.102732</v>
+        <v>36.104476</v>
       </c>
     </row>
     <row r="1226" spans="1:5">
@@ -26315,10 +26313,10 @@
         <v>78</v>
       </c>
       <c r="D1226">
-        <v>120.39126</v>
+        <v>117.117615</v>
       </c>
       <c r="E1226">
-        <v>36.104476</v>
+        <v>36.683182</v>
       </c>
     </row>
     <row r="1227" spans="1:5">
@@ -26332,10 +26330,10 @@
         <v>78</v>
       </c>
       <c r="D1227">
-        <v>117.117615</v>
+        <v>117.122829</v>
       </c>
       <c r="E1227">
-        <v>36.683182</v>
+        <v>36.690321</v>
       </c>
     </row>
     <row r="1228" spans="1:5">
@@ -26349,10 +26347,10 @@
         <v>78</v>
       </c>
       <c r="D1228">
-        <v>117.122829</v>
+        <v>117.155626</v>
       </c>
       <c r="E1228">
-        <v>36.690321</v>
+        <v>36.659698</v>
       </c>
     </row>
     <row r="1229" spans="1:5">
@@ -26366,10 +26364,10 @@
         <v>78</v>
       </c>
       <c r="D1229">
-        <v>117.155626</v>
+        <v>117.112292</v>
       </c>
       <c r="E1229">
-        <v>36.659698</v>
+        <v>36.683335</v>
       </c>
     </row>
     <row r="1230" spans="1:5">
@@ -26383,10 +26381,10 @@
         <v>78</v>
       </c>
       <c r="D1230">
-        <v>117.112292</v>
+        <v>117.133541</v>
       </c>
       <c r="E1230">
-        <v>36.683335</v>
+        <v>36.65746</v>
       </c>
     </row>
     <row r="1231" spans="1:5">
@@ -26397,13 +26395,13 @@
         <v>6</v>
       </c>
       <c r="C1231" t="s">
-        <v>78</v>
+        <v>13</v>
       </c>
       <c r="D1231">
-        <v>117.133541</v>
+        <v>108.961923</v>
       </c>
       <c r="E1231">
-        <v>36.65746</v>
+        <v>34.245875</v>
       </c>
     </row>
     <row r="1232" spans="1:5">
@@ -26417,10 +26415,10 @@
         <v>13</v>
       </c>
       <c r="D1232">
-        <v>108.961923</v>
+        <v>109.015101</v>
       </c>
       <c r="E1232">
-        <v>34.245875</v>
+        <v>34.331159</v>
       </c>
     </row>
     <row r="1233" spans="1:5">
@@ -26431,13 +26429,13 @@
         <v>6</v>
       </c>
       <c r="C1233" t="s">
-        <v>13</v>
+        <v>297</v>
       </c>
       <c r="D1233">
-        <v>109.015101</v>
+        <v>115.557425</v>
       </c>
       <c r="E1233">
-        <v>34.331159</v>
+        <v>28.060112</v>
       </c>
     </row>
     <row r="1234" spans="1:5">
@@ -26448,13 +26446,13 @@
         <v>6</v>
       </c>
       <c r="C1234" t="s">
-        <v>297</v>
+        <v>139</v>
       </c>
       <c r="D1234">
-        <v>115.557425</v>
+        <v>125.33683</v>
       </c>
       <c r="E1234">
-        <v>28.060112</v>
+        <v>43.904214</v>
       </c>
     </row>
     <row r="1235" spans="1:5">
@@ -26465,13 +26463,13 @@
         <v>6</v>
       </c>
       <c r="C1235" t="s">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="D1235">
-        <v>125.33683</v>
+        <v>116.346058</v>
       </c>
       <c r="E1235">
-        <v>43.904214</v>
+        <v>39.758018</v>
       </c>
     </row>
     <row r="1236" spans="1:5">
@@ -26482,13 +26480,13 @@
         <v>6</v>
       </c>
       <c r="C1236" t="s">
-        <v>45</v>
+        <v>91</v>
       </c>
       <c r="D1236">
-        <v>116.346058</v>
+        <v>120.835664</v>
       </c>
       <c r="E1236">
-        <v>39.758018</v>
+        <v>40.698934</v>
       </c>
     </row>
     <row r="1237" spans="1:5">
@@ -26499,13 +26497,13 @@
         <v>6</v>
       </c>
       <c r="C1237" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D1237">
-        <v>120.835664</v>
+        <v>118.617646</v>
       </c>
       <c r="E1237">
-        <v>40.698934</v>
+        <v>24.890463</v>
       </c>
     </row>
     <row r="1238" spans="1:5">
@@ -26519,10 +26517,10 @@
         <v>35</v>
       </c>
       <c r="D1238">
-        <v>118.617646</v>
+        <v>118.62452</v>
       </c>
       <c r="E1238">
-        <v>24.890463</v>
+        <v>24.73856</v>
       </c>
     </row>
     <row r="1239" spans="1:5">
@@ -26533,13 +26531,13 @@
         <v>6</v>
       </c>
       <c r="C1239" t="s">
-        <v>35</v>
+        <v>207</v>
       </c>
       <c r="D1239">
-        <v>118.62452</v>
+        <v>117.271767</v>
       </c>
       <c r="E1239">
-        <v>24.73856</v>
+        <v>31.886751</v>
       </c>
     </row>
     <row r="1240" spans="1:5">
@@ -26550,13 +26548,13 @@
         <v>6</v>
       </c>
       <c r="C1240" t="s">
-        <v>207</v>
+        <v>78</v>
       </c>
       <c r="D1240">
-        <v>117.271767</v>
+        <v>117.138923</v>
       </c>
       <c r="E1240">
-        <v>31.886751</v>
+        <v>36.719252</v>
       </c>
     </row>
     <row r="1241" spans="1:5">
@@ -26570,10 +26568,10 @@
         <v>78</v>
       </c>
       <c r="D1241">
-        <v>117.138923</v>
+        <v>116.807399</v>
       </c>
       <c r="E1241">
-        <v>36.719252</v>
+        <v>36.509118</v>
       </c>
     </row>
     <row r="1242" spans="1:5">
@@ -26587,10 +26585,10 @@
         <v>78</v>
       </c>
       <c r="D1242">
-        <v>116.807399</v>
+        <v>117.076943</v>
       </c>
       <c r="E1242">
-        <v>36.509118</v>
+        <v>36.701072</v>
       </c>
     </row>
     <row r="1243" spans="1:5">
@@ -26604,10 +26602,10 @@
         <v>78</v>
       </c>
       <c r="D1243">
-        <v>117.076943</v>
+        <v>117.063017</v>
       </c>
       <c r="E1243">
-        <v>36.701072</v>
+        <v>36.682424</v>
       </c>
     </row>
     <row r="1244" spans="1:5">
@@ -26621,10 +26619,10 @@
         <v>78</v>
       </c>
       <c r="D1244">
-        <v>117.063017</v>
+        <v>117.072781</v>
       </c>
       <c r="E1244">
-        <v>36.682424</v>
+        <v>36.665435</v>
       </c>
     </row>
     <row r="1245" spans="1:5">
@@ -26638,10 +26636,10 @@
         <v>78</v>
       </c>
       <c r="D1245">
-        <v>117.072781</v>
+        <v>117.228378</v>
       </c>
       <c r="E1245">
-        <v>36.665435</v>
+        <v>36.695597</v>
       </c>
     </row>
     <row r="1246" spans="1:5">
@@ -26655,10 +26653,10 @@
         <v>78</v>
       </c>
       <c r="D1246">
-        <v>117.228378</v>
+        <v>117.073754</v>
       </c>
       <c r="E1246">
-        <v>36.695597</v>
+        <v>36.740943</v>
       </c>
     </row>
     <row r="1247" spans="1:5">
@@ -26672,10 +26670,10 @@
         <v>78</v>
       </c>
       <c r="D1247">
-        <v>117.073754</v>
+        <v>117.164187</v>
       </c>
       <c r="E1247">
-        <v>36.740943</v>
+        <v>36.651885</v>
       </c>
     </row>
     <row r="1248" spans="1:5">
@@ -26689,10 +26687,10 @@
         <v>78</v>
       </c>
       <c r="D1248">
-        <v>117.164187</v>
+        <v>117.129466</v>
       </c>
       <c r="E1248">
-        <v>36.651885</v>
+        <v>36.681899</v>
       </c>
     </row>
     <row r="1249" spans="1:5">
@@ -26706,10 +26704,10 @@
         <v>78</v>
       </c>
       <c r="D1249">
-        <v>117.129466</v>
+        <v>117.152519</v>
       </c>
       <c r="E1249">
-        <v>36.681899</v>
+        <v>36.653104</v>
       </c>
     </row>
     <row r="1250" spans="1:5">
@@ -26720,13 +26718,13 @@
         <v>6</v>
       </c>
       <c r="C1250" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="D1250">
-        <v>117.152519</v>
+        <v>117.660893</v>
       </c>
       <c r="E1250">
-        <v>36.653104</v>
+        <v>24.518847</v>
       </c>
     </row>
     <row r="1251" spans="1:5">
@@ -26737,13 +26735,13 @@
         <v>6</v>
       </c>
       <c r="C1251" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D1251">
-        <v>117.660893</v>
+        <v>108.962499</v>
       </c>
       <c r="E1251">
-        <v>24.518847</v>
+        <v>34.221815</v>
       </c>
     </row>
     <row r="1252" spans="1:5">
@@ -26751,16 +26749,16 @@
         <v>1286</v>
       </c>
       <c r="B1252" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1252" t="s">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="D1252">
-        <v>108.962499</v>
+        <v>121.872253</v>
       </c>
       <c r="E1252">
-        <v>34.221815</v>
+        <v>29.447744</v>
       </c>
     </row>
     <row r="1253" spans="1:5">
@@ -26768,16 +26766,16 @@
         <v>1287</v>
       </c>
       <c r="B1253" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1253" t="s">
-        <v>94</v>
+        <v>45</v>
       </c>
       <c r="D1253">
-        <v>121.872253</v>
+        <v>116.314501</v>
       </c>
       <c r="E1253">
-        <v>29.447744</v>
+        <v>39.997771</v>
       </c>
     </row>
     <row r="1254" spans="1:5">
@@ -26788,13 +26786,13 @@
         <v>6</v>
       </c>
       <c r="C1254" t="s">
-        <v>45</v>
+        <v>297</v>
       </c>
       <c r="D1254">
-        <v>116.314501</v>
+        <v>115.896521</v>
       </c>
       <c r="E1254">
-        <v>39.997771</v>
+        <v>28.689578</v>
       </c>
     </row>
     <row r="1255" spans="1:5">
@@ -26805,13 +26803,13 @@
         <v>6</v>
       </c>
       <c r="C1255" t="s">
-        <v>297</v>
+        <v>22</v>
       </c>
       <c r="D1255">
-        <v>115.896521</v>
+        <v>114.887983</v>
       </c>
       <c r="E1255">
-        <v>28.689578</v>
+        <v>30.450961</v>
       </c>
     </row>
     <row r="1256" spans="1:5">
@@ -26822,13 +26820,13 @@
         <v>6</v>
       </c>
       <c r="C1256" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="D1256">
-        <v>114.887983</v>
+        <v>120.398272</v>
       </c>
       <c r="E1256">
-        <v>30.450961</v>
+        <v>36.122687</v>
       </c>
     </row>
     <row r="1257" spans="1:5">
@@ -26842,10 +26840,10 @@
         <v>78</v>
       </c>
       <c r="D1257">
-        <v>120.398272</v>
+        <v>120.401097</v>
       </c>
       <c r="E1257">
-        <v>36.122687</v>
+        <v>36.122476</v>
       </c>
     </row>
     <row r="1258" spans="1:5">
@@ -26859,10 +26857,10 @@
         <v>78</v>
       </c>
       <c r="D1258">
-        <v>120.401097</v>
+        <v>120.381969</v>
       </c>
       <c r="E1258">
-        <v>36.122476</v>
+        <v>36.117807</v>
       </c>
     </row>
     <row r="1259" spans="1:5">
@@ -26876,10 +26874,10 @@
         <v>78</v>
       </c>
       <c r="D1259">
-        <v>120.381969</v>
+        <v>120.384847</v>
       </c>
       <c r="E1259">
-        <v>36.117807</v>
+        <v>36.121382</v>
       </c>
     </row>
     <row r="1260" spans="1:5">
@@ -26893,10 +26891,10 @@
         <v>78</v>
       </c>
       <c r="D1260">
-        <v>120.384847</v>
+        <v>120.40697</v>
       </c>
       <c r="E1260">
-        <v>36.121382</v>
+        <v>36.130848</v>
       </c>
     </row>
     <row r="1261" spans="1:5">
@@ -26910,10 +26908,10 @@
         <v>78</v>
       </c>
       <c r="D1261">
-        <v>120.40697</v>
+        <v>120.396118</v>
       </c>
       <c r="E1261">
-        <v>36.130848</v>
+        <v>36.137831</v>
       </c>
     </row>
     <row r="1262" spans="1:5">
@@ -26927,10 +26925,10 @@
         <v>78</v>
       </c>
       <c r="D1262">
-        <v>120.396118</v>
+        <v>120.389222</v>
       </c>
       <c r="E1262">
-        <v>36.137831</v>
+        <v>36.140945</v>
       </c>
     </row>
     <row r="1263" spans="1:5">
@@ -26944,10 +26942,10 @@
         <v>78</v>
       </c>
       <c r="D1263">
-        <v>120.389222</v>
+        <v>120.342526</v>
       </c>
       <c r="E1263">
-        <v>36.140945</v>
+        <v>36.120968</v>
       </c>
     </row>
     <row r="1264" spans="1:5">
@@ -26961,10 +26959,10 @@
         <v>78</v>
       </c>
       <c r="D1264">
-        <v>120.342526</v>
+        <v>120.359896</v>
       </c>
       <c r="E1264">
-        <v>36.120968</v>
+        <v>36.12777</v>
       </c>
     </row>
     <row r="1265" spans="1:5">
@@ -26978,10 +26976,10 @@
         <v>78</v>
       </c>
       <c r="D1265">
-        <v>120.359896</v>
+        <v>120.374432</v>
       </c>
       <c r="E1265">
-        <v>36.12777</v>
+        <v>36.133719</v>
       </c>
     </row>
     <row r="1266" spans="1:5">
@@ -26995,10 +26993,10 @@
         <v>78</v>
       </c>
       <c r="D1266">
-        <v>120.374432</v>
+        <v>120.385291</v>
       </c>
       <c r="E1266">
-        <v>36.133719</v>
+        <v>36.174489</v>
       </c>
     </row>
     <row r="1267" spans="1:5">
@@ -27012,10 +27010,10 @@
         <v>78</v>
       </c>
       <c r="D1267">
-        <v>120.385291</v>
+        <v>120.378829</v>
       </c>
       <c r="E1267">
-        <v>36.174489</v>
+        <v>36.187844</v>
       </c>
     </row>
     <row r="1268" spans="1:5">
@@ -27029,10 +27027,10 @@
         <v>78</v>
       </c>
       <c r="D1268">
-        <v>120.378829</v>
+        <v>120.435545</v>
       </c>
       <c r="E1268">
-        <v>36.187844</v>
+        <v>36.313502</v>
       </c>
     </row>
     <row r="1269" spans="1:5">
@@ -27046,10 +27044,10 @@
         <v>78</v>
       </c>
       <c r="D1269">
-        <v>120.435545</v>
+        <v>120.413228</v>
       </c>
       <c r="E1269">
-        <v>36.313502</v>
+        <v>36.302294</v>
       </c>
     </row>
     <row r="1270" spans="1:5">
@@ -27063,10 +27061,10 @@
         <v>78</v>
       </c>
       <c r="D1270">
-        <v>120.413228</v>
+        <v>120.399696</v>
       </c>
       <c r="E1270">
-        <v>36.302294</v>
+        <v>36.28358</v>
       </c>
     </row>
     <row r="1271" spans="1:5">
@@ -27080,10 +27078,10 @@
         <v>78</v>
       </c>
       <c r="D1271">
-        <v>120.399696</v>
+        <v>120.38482</v>
       </c>
       <c r="E1271">
-        <v>36.28358</v>
+        <v>36.30069</v>
       </c>
     </row>
     <row r="1272" spans="1:5">
@@ -27097,10 +27095,10 @@
         <v>78</v>
       </c>
       <c r="D1272">
-        <v>120.38482</v>
+        <v>120.319718</v>
       </c>
       <c r="E1272">
-        <v>36.30069</v>
+        <v>36.081054</v>
       </c>
     </row>
     <row r="1273" spans="1:5">
@@ -27114,10 +27112,10 @@
         <v>78</v>
       </c>
       <c r="D1273">
-        <v>120.319718</v>
+        <v>120.315396</v>
       </c>
       <c r="E1273">
-        <v>36.081054</v>
+        <v>36.079735</v>
       </c>
     </row>
     <row r="1274" spans="1:5">
@@ -27131,10 +27129,10 @@
         <v>78</v>
       </c>
       <c r="D1274">
-        <v>120.315396</v>
+        <v>120.166804</v>
       </c>
       <c r="E1274">
-        <v>36.079735</v>
+        <v>35.923625</v>
       </c>
     </row>
     <row r="1275" spans="1:5">
@@ -27148,10 +27146,10 @@
         <v>78</v>
       </c>
       <c r="D1275">
-        <v>120.166804</v>
+        <v>119.1247</v>
       </c>
       <c r="E1275">
-        <v>35.923625</v>
+        <v>36.707511</v>
       </c>
     </row>
     <row r="1276" spans="1:5">
@@ -27165,10 +27163,10 @@
         <v>78</v>
       </c>
       <c r="D1276">
-        <v>119.1247</v>
+        <v>119.113599</v>
       </c>
       <c r="E1276">
-        <v>36.707511</v>
+        <v>36.709491</v>
       </c>
     </row>
     <row r="1277" spans="1:5">
@@ -27182,10 +27180,10 @@
         <v>78</v>
       </c>
       <c r="D1277">
-        <v>119.113599</v>
+        <v>119.130715</v>
       </c>
       <c r="E1277">
-        <v>36.709491</v>
+        <v>36.719045</v>
       </c>
     </row>
     <row r="1278" spans="1:5">
@@ -27199,10 +27197,10 @@
         <v>78</v>
       </c>
       <c r="D1278">
-        <v>119.130715</v>
+        <v>119.12141</v>
       </c>
       <c r="E1278">
-        <v>36.719045</v>
+        <v>36.692894</v>
       </c>
     </row>
     <row r="1279" spans="1:5">
@@ -27216,10 +27214,10 @@
         <v>78</v>
       </c>
       <c r="D1279">
-        <v>119.12141</v>
+        <v>119.090486</v>
       </c>
       <c r="E1279">
-        <v>36.692894</v>
+        <v>36.73413</v>
       </c>
     </row>
     <row r="1280" spans="1:5">
@@ -27233,10 +27231,10 @@
         <v>78</v>
       </c>
       <c r="D1280">
-        <v>119.090486</v>
+        <v>119.126719</v>
       </c>
       <c r="E1280">
-        <v>36.73413</v>
+        <v>36.707113</v>
       </c>
     </row>
     <row r="1281" spans="1:5">
@@ -27250,10 +27248,10 @@
         <v>78</v>
       </c>
       <c r="D1281">
-        <v>119.126719</v>
+        <v>120.160388</v>
       </c>
       <c r="E1281">
-        <v>36.707113</v>
+        <v>35.950252</v>
       </c>
     </row>
     <row r="1282" spans="1:5">
@@ -27264,13 +27262,13 @@
         <v>6</v>
       </c>
       <c r="C1282" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="D1282">
-        <v>120.160388</v>
+        <v>113.562115</v>
       </c>
       <c r="E1282">
-        <v>35.950252</v>
+        <v>34.824999</v>
       </c>
     </row>
     <row r="1283" spans="1:5">
@@ -27281,13 +27279,13 @@
         <v>6</v>
       </c>
       <c r="C1283" t="s">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="D1283">
-        <v>113.562115</v>
+        <v>105.452975</v>
       </c>
       <c r="E1283">
-        <v>34.824999</v>
+        <v>27.227563</v>
       </c>
     </row>
     <row r="1284" spans="1:5">
@@ -27295,16 +27293,16 @@
         <v>1318</v>
       </c>
       <c r="B1284" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1284" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="D1284">
-        <v>105.452975</v>
+        <v>118.888916</v>
       </c>
       <c r="E1284">
-        <v>27.227563</v>
+        <v>32.155473</v>
       </c>
     </row>
     <row r="1285" spans="1:5">
@@ -27315,13 +27313,13 @@
         <v>74</v>
       </c>
       <c r="C1285" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D1285">
-        <v>118.888916</v>
+        <v>117.097001</v>
       </c>
       <c r="E1285">
-        <v>32.155473</v>
+        <v>36.667995</v>
       </c>
     </row>
     <row r="1286" spans="1:5">
@@ -27329,16 +27327,16 @@
         <v>1320</v>
       </c>
       <c r="B1286" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1286" t="s">
-        <v>78</v>
+        <v>94</v>
       </c>
       <c r="D1286">
-        <v>117.097001</v>
+        <v>120.283906</v>
       </c>
       <c r="E1286">
-        <v>36.667995</v>
+        <v>30.407107</v>
       </c>
     </row>
     <row r="1287" spans="1:5">
@@ -27352,10 +27350,10 @@
         <v>94</v>
       </c>
       <c r="D1287">
-        <v>120.283906</v>
+        <v>120.082374</v>
       </c>
       <c r="E1287">
-        <v>30.407107</v>
+        <v>30.151354</v>
       </c>
     </row>
     <row r="1288" spans="1:5">
@@ -27369,10 +27367,10 @@
         <v>94</v>
       </c>
       <c r="D1288">
-        <v>120.082374</v>
+        <v>120.255082</v>
       </c>
       <c r="E1288">
-        <v>30.151354</v>
+        <v>30.180185</v>
       </c>
     </row>
     <row r="1289" spans="1:5">
@@ -27380,16 +27378,16 @@
         <v>1323</v>
       </c>
       <c r="B1289" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1289" t="s">
-        <v>94</v>
+        <v>225</v>
       </c>
       <c r="D1289">
-        <v>120.255082</v>
+        <v>112.569887</v>
       </c>
       <c r="E1289">
-        <v>30.180185</v>
+        <v>37.824541</v>
       </c>
     </row>
     <row r="1290" spans="1:5">
@@ -27400,13 +27398,13 @@
         <v>74</v>
       </c>
       <c r="C1290" t="s">
-        <v>225</v>
+        <v>94</v>
       </c>
       <c r="D1290">
-        <v>112.569887</v>
+        <v>120.221347</v>
       </c>
       <c r="E1290">
-        <v>37.824541</v>
+        <v>30.207405</v>
       </c>
     </row>
     <row r="1291" spans="1:5">
@@ -27414,16 +27412,16 @@
         <v>1325</v>
       </c>
       <c r="B1291" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1291" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="D1291">
-        <v>120.221347</v>
+        <v>108.754313</v>
       </c>
       <c r="E1291">
-        <v>30.207405</v>
+        <v>34.318963</v>
       </c>
     </row>
     <row r="1292" spans="1:5">
@@ -27434,13 +27432,13 @@
         <v>6</v>
       </c>
       <c r="C1292" t="s">
-        <v>13</v>
+        <v>91</v>
       </c>
       <c r="D1292">
-        <v>108.754313</v>
+        <v>121.654949</v>
       </c>
       <c r="E1292">
-        <v>34.318963</v>
+        <v>38.927818</v>
       </c>
     </row>
     <row r="1293" spans="1:5">
@@ -27454,10 +27452,10 @@
         <v>91</v>
       </c>
       <c r="D1293">
-        <v>121.654949</v>
+        <v>121.632821</v>
       </c>
       <c r="E1293">
-        <v>38.927818</v>
+        <v>38.918934</v>
       </c>
     </row>
     <row r="1294" spans="1:5">
@@ -27471,10 +27469,10 @@
         <v>91</v>
       </c>
       <c r="D1294">
-        <v>121.632821</v>
+        <v>121.518989</v>
       </c>
       <c r="E1294">
-        <v>38.918934</v>
+        <v>38.847725</v>
       </c>
     </row>
     <row r="1295" spans="1:5">
@@ -27488,10 +27486,10 @@
         <v>91</v>
       </c>
       <c r="D1295">
-        <v>121.518989</v>
+        <v>121.448143</v>
       </c>
       <c r="E1295">
-        <v>38.847725</v>
+        <v>38.859488</v>
       </c>
     </row>
     <row r="1296" spans="1:5">
@@ -27505,10 +27503,10 @@
         <v>91</v>
       </c>
       <c r="D1296">
-        <v>121.448143</v>
+        <v>121.578688</v>
       </c>
       <c r="E1296">
-        <v>38.859488</v>
+        <v>38.881726</v>
       </c>
     </row>
     <row r="1297" spans="1:5">
@@ -27522,10 +27520,10 @@
         <v>91</v>
       </c>
       <c r="D1297">
-        <v>121.578688</v>
+        <v>121.587121</v>
       </c>
       <c r="E1297">
-        <v>38.881726</v>
+        <v>38.890637</v>
       </c>
     </row>
     <row r="1298" spans="1:5">
@@ -27536,13 +27534,13 @@
         <v>6</v>
       </c>
       <c r="C1298" t="s">
-        <v>91</v>
+        <v>35</v>
       </c>
       <c r="D1298">
-        <v>121.587121</v>
+        <v>117.010228</v>
       </c>
       <c r="E1298">
-        <v>38.890637</v>
+        <v>25.11149</v>
       </c>
     </row>
     <row r="1299" spans="1:5">
@@ -27553,13 +27551,13 @@
         <v>6</v>
       </c>
       <c r="C1299" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="D1299">
-        <v>117.010228</v>
+        <v>114.759055</v>
       </c>
       <c r="E1299">
-        <v>25.11149</v>
+        <v>37.352349</v>
       </c>
     </row>
     <row r="1300" spans="1:5">
@@ -27570,13 +27568,13 @@
         <v>6</v>
       </c>
       <c r="C1300" t="s">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="D1300">
-        <v>114.759055</v>
+        <v>119.994255</v>
       </c>
       <c r="E1300">
-        <v>37.352349</v>
+        <v>35.816989</v>
       </c>
     </row>
     <row r="1301" spans="1:5">
@@ -27587,13 +27585,13 @@
         <v>6</v>
       </c>
       <c r="C1301" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D1301">
-        <v>119.994255</v>
+        <v>120.358873</v>
       </c>
       <c r="E1301">
-        <v>35.816989</v>
+        <v>31.584977</v>
       </c>
     </row>
     <row r="1302" spans="1:5">
@@ -27604,13 +27602,13 @@
         <v>6</v>
       </c>
       <c r="C1302" t="s">
-        <v>97</v>
+        <v>225</v>
       </c>
       <c r="D1302">
-        <v>120.358873</v>
+        <v>112.506426</v>
       </c>
       <c r="E1302">
-        <v>31.584977</v>
+        <v>37.839288</v>
       </c>
     </row>
     <row r="1303" spans="1:5">
@@ -27618,16 +27616,16 @@
         <v>1337</v>
       </c>
       <c r="B1303" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1303" t="s">
-        <v>225</v>
+        <v>83</v>
       </c>
       <c r="D1303">
-        <v>112.506426</v>
+        <v>102.712061</v>
       </c>
       <c r="E1303">
-        <v>37.839288</v>
+        <v>25.008496</v>
       </c>
     </row>
     <row r="1304" spans="1:5">
@@ -27638,13 +27636,13 @@
         <v>74</v>
       </c>
       <c r="C1304" t="s">
-        <v>83</v>
+        <v>297</v>
       </c>
       <c r="D1304">
-        <v>102.712061</v>
+        <v>115.852638</v>
       </c>
       <c r="E1304">
-        <v>25.008496</v>
+        <v>28.684449</v>
       </c>
     </row>
     <row r="1305" spans="1:5">
@@ -27655,13 +27653,13 @@
         <v>74</v>
       </c>
       <c r="C1305" t="s">
-        <v>297</v>
+        <v>7</v>
       </c>
       <c r="D1305">
-        <v>115.852638</v>
+        <v>104.460005</v>
       </c>
       <c r="E1305">
-        <v>28.684449</v>
+        <v>30.850199</v>
       </c>
     </row>
     <row r="1306" spans="1:5">
@@ -27672,13 +27670,13 @@
         <v>74</v>
       </c>
       <c r="C1306" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D1306">
-        <v>104.460005</v>
+        <v>108.885677</v>
       </c>
       <c r="E1306">
-        <v>30.850199</v>
+        <v>34.195711</v>
       </c>
     </row>
     <row r="1307" spans="1:5">
@@ -27686,16 +27684,16 @@
         <v>1341</v>
       </c>
       <c r="B1307" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1307" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D1307">
-        <v>108.885677</v>
+        <v>114.329742</v>
       </c>
       <c r="E1307">
-        <v>34.195711</v>
+        <v>30.58895</v>
       </c>
     </row>
     <row r="1308" spans="1:5">
@@ -27706,13 +27704,13 @@
         <v>6</v>
       </c>
       <c r="C1308" t="s">
-        <v>22</v>
+        <v>78</v>
       </c>
       <c r="D1308">
-        <v>114.329742</v>
+        <v>117.071932</v>
       </c>
       <c r="E1308">
-        <v>30.58895</v>
+        <v>36.692878</v>
       </c>
     </row>
     <row r="1309" spans="1:5">
@@ -27723,13 +27721,13 @@
         <v>6</v>
       </c>
       <c r="C1309" t="s">
-        <v>78</v>
+        <v>35</v>
       </c>
       <c r="D1309">
-        <v>117.071932</v>
+        <v>118.018232</v>
       </c>
       <c r="E1309">
-        <v>36.692878</v>
+        <v>24.612171</v>
       </c>
     </row>
     <row r="1310" spans="1:5">
@@ -27740,13 +27738,13 @@
         <v>6</v>
       </c>
       <c r="C1310" t="s">
-        <v>35</v>
+        <v>297</v>
       </c>
       <c r="D1310">
-        <v>118.018232</v>
+        <v>115.969767</v>
       </c>
       <c r="E1310">
-        <v>24.612171</v>
+        <v>28.712084</v>
       </c>
     </row>
     <row r="1311" spans="1:5">
@@ -27754,16 +27752,16 @@
         <v>1345</v>
       </c>
       <c r="B1311" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1311" t="s">
-        <v>297</v>
+        <v>139</v>
       </c>
       <c r="D1311">
-        <v>115.969767</v>
+        <v>125.386502</v>
       </c>
       <c r="E1311">
-        <v>28.712084</v>
+        <v>43.797794</v>
       </c>
     </row>
     <row r="1312" spans="1:5">
@@ -27774,13 +27772,13 @@
         <v>74</v>
       </c>
       <c r="C1312" t="s">
-        <v>139</v>
+        <v>45</v>
       </c>
       <c r="D1312">
-        <v>125.386502</v>
+        <v>116.348594</v>
       </c>
       <c r="E1312">
-        <v>43.797794</v>
+        <v>40.090213</v>
       </c>
     </row>
     <row r="1313" spans="1:5">
@@ -27791,13 +27789,13 @@
         <v>74</v>
       </c>
       <c r="C1313" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D1313">
-        <v>116.348594</v>
+        <v>115.511939</v>
       </c>
       <c r="E1313">
-        <v>40.090213</v>
+        <v>35.859008</v>
       </c>
     </row>
     <row r="1314" spans="1:5">
@@ -27805,16 +27803,16 @@
         <v>1348</v>
       </c>
       <c r="B1314" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1314" t="s">
-        <v>38</v>
+        <v>297</v>
       </c>
       <c r="D1314">
-        <v>115.511939</v>
+        <v>116.020928</v>
       </c>
       <c r="E1314">
-        <v>35.859008</v>
+        <v>28.6736</v>
       </c>
     </row>
     <row r="1315" spans="1:5">
@@ -27825,13 +27823,13 @@
         <v>6</v>
       </c>
       <c r="C1315" t="s">
-        <v>297</v>
+        <v>22</v>
       </c>
       <c r="D1315">
-        <v>116.020928</v>
+        <v>114.349415</v>
       </c>
       <c r="E1315">
-        <v>28.6736</v>
+        <v>30.564509</v>
       </c>
     </row>
     <row r="1316" spans="1:5">
@@ -27842,13 +27840,13 @@
         <v>6</v>
       </c>
       <c r="C1316" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="D1316">
-        <v>114.349415</v>
+        <v>116.451879</v>
       </c>
       <c r="E1316">
-        <v>30.564509</v>
+        <v>33.942039</v>
       </c>
     </row>
     <row r="1317" spans="1:5">
@@ -27862,10 +27860,10 @@
         <v>38</v>
       </c>
       <c r="D1317">
-        <v>116.451879</v>
+        <v>115.704239</v>
       </c>
       <c r="E1317">
-        <v>33.942039</v>
+        <v>34.377516</v>
       </c>
     </row>
     <row r="1318" spans="1:5">
@@ -27879,10 +27877,10 @@
         <v>38</v>
       </c>
       <c r="D1318">
-        <v>115.704239</v>
+        <v>115.65169</v>
       </c>
       <c r="E1318">
-        <v>34.377516</v>
+        <v>34.42061</v>
       </c>
     </row>
     <row r="1319" spans="1:5">
@@ -27893,13 +27891,13 @@
         <v>6</v>
       </c>
       <c r="C1319" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D1319">
-        <v>115.65169</v>
+        <v>118.606169</v>
       </c>
       <c r="E1319">
-        <v>34.42061</v>
+        <v>24.885053</v>
       </c>
     </row>
     <row r="1320" spans="1:5">
@@ -27913,10 +27911,10 @@
         <v>35</v>
       </c>
       <c r="D1320">
-        <v>118.606169</v>
+        <v>118.654762</v>
       </c>
       <c r="E1320">
-        <v>24.885053</v>
+        <v>24.922828</v>
       </c>
     </row>
     <row r="1321" spans="1:5">
@@ -27930,10 +27928,10 @@
         <v>35</v>
       </c>
       <c r="D1321">
-        <v>118.654762</v>
+        <v>118.078792</v>
       </c>
       <c r="E1321">
-        <v>24.922828</v>
+        <v>24.465792</v>
       </c>
     </row>
     <row r="1322" spans="1:5">
@@ -27947,10 +27945,10 @@
         <v>35</v>
       </c>
       <c r="D1322">
-        <v>118.078792</v>
+        <v>118.087217</v>
       </c>
       <c r="E1322">
-        <v>24.465792</v>
+        <v>24.477684</v>
       </c>
     </row>
     <row r="1323" spans="1:5">
@@ -27964,10 +27962,10 @@
         <v>35</v>
       </c>
       <c r="D1323">
-        <v>118.087217</v>
+        <v>118.072892</v>
       </c>
       <c r="E1323">
-        <v>24.477684</v>
+        <v>24.457956</v>
       </c>
     </row>
     <row r="1324" spans="1:5">
@@ -27981,10 +27979,10 @@
         <v>35</v>
       </c>
       <c r="D1324">
-        <v>118.072892</v>
+        <v>118.11402</v>
       </c>
       <c r="E1324">
-        <v>24.457956</v>
+        <v>24.478387</v>
       </c>
     </row>
     <row r="1325" spans="1:5">
@@ -27998,10 +27996,10 @@
         <v>35</v>
       </c>
       <c r="D1325">
-        <v>118.11402</v>
+        <v>118.087328</v>
       </c>
       <c r="E1325">
-        <v>24.478387</v>
+        <v>24.439849</v>
       </c>
     </row>
     <row r="1326" spans="1:5">
@@ -28012,13 +28010,13 @@
         <v>6</v>
       </c>
       <c r="C1326" t="s">
-        <v>35</v>
+        <v>13</v>
       </c>
       <c r="D1326">
-        <v>118.087328</v>
+        <v>108.82475</v>
       </c>
       <c r="E1326">
-        <v>24.439849</v>
+        <v>34.29357</v>
       </c>
     </row>
     <row r="1327" spans="1:5">
@@ -28026,16 +28024,16 @@
         <v>1361</v>
       </c>
       <c r="B1327" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1327" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="D1327">
-        <v>108.82475</v>
+        <v>112.853016</v>
       </c>
       <c r="E1327">
-        <v>34.29357</v>
+        <v>23.206266</v>
       </c>
     </row>
     <row r="1328" spans="1:5">
@@ -28046,13 +28044,13 @@
         <v>74</v>
       </c>
       <c r="C1328" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="D1328">
-        <v>112.853016</v>
+        <v>121.59215</v>
       </c>
       <c r="E1328">
-        <v>23.206266</v>
+        <v>38.92327</v>
       </c>
     </row>
     <row r="1329" spans="1:5">
@@ -28060,16 +28058,16 @@
         <v>1363</v>
       </c>
       <c r="B1329" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1329" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="D1329">
-        <v>121.59215</v>
+        <v>108.920408</v>
       </c>
       <c r="E1329">
-        <v>38.92327</v>
+        <v>34.286895</v>
       </c>
     </row>
     <row r="1330" spans="1:5">
@@ -28077,16 +28075,16 @@
         <v>1364</v>
       </c>
       <c r="B1330" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1330" t="s">
-        <v>13</v>
+        <v>148</v>
       </c>
       <c r="D1330">
-        <v>108.920408</v>
+        <v>108.354826</v>
       </c>
       <c r="E1330">
-        <v>34.286895</v>
+        <v>22.825707</v>
       </c>
     </row>
     <row r="1331" spans="1:5">
@@ -28097,13 +28095,13 @@
         <v>74</v>
       </c>
       <c r="C1331" t="s">
-        <v>148</v>
+        <v>20</v>
       </c>
       <c r="D1331">
-        <v>108.354826</v>
+        <v>113.940001</v>
       </c>
       <c r="E1331">
-        <v>22.825707</v>
+        <v>22.523889</v>
       </c>
     </row>
     <row r="1332" spans="1:5">
@@ -28111,16 +28109,16 @@
         <v>1366</v>
       </c>
       <c r="B1332" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1332" t="s">
-        <v>20</v>
+        <v>91</v>
       </c>
       <c r="D1332">
-        <v>113.940001</v>
+        <v>121.74382</v>
       </c>
       <c r="E1332">
-        <v>22.523889</v>
+        <v>39.048027</v>
       </c>
     </row>
     <row r="1333" spans="1:5">
@@ -28134,10 +28132,10 @@
         <v>91</v>
       </c>
       <c r="D1333">
-        <v>121.74382</v>
+        <v>124.365224</v>
       </c>
       <c r="E1333">
-        <v>39.048027</v>
+        <v>40.111661</v>
       </c>
     </row>
     <row r="1334" spans="1:5">
@@ -28151,10 +28149,10 @@
         <v>91</v>
       </c>
       <c r="D1334">
-        <v>124.365224</v>
+        <v>121.577005</v>
       </c>
       <c r="E1334">
-        <v>40.111661</v>
+        <v>38.901093</v>
       </c>
     </row>
     <row r="1335" spans="1:5">
@@ -28168,10 +28166,10 @@
         <v>91</v>
       </c>
       <c r="D1335">
-        <v>121.577005</v>
+        <v>124.345098</v>
       </c>
       <c r="E1335">
-        <v>38.901093</v>
+        <v>40.012615</v>
       </c>
     </row>
     <row r="1336" spans="1:5">
@@ -28185,10 +28183,10 @@
         <v>91</v>
       </c>
       <c r="D1336">
-        <v>124.345098</v>
+        <v>121.588501</v>
       </c>
       <c r="E1336">
-        <v>40.012615</v>
+        <v>38.924801</v>
       </c>
     </row>
     <row r="1337" spans="1:5">
@@ -28202,10 +28200,10 @@
         <v>91</v>
       </c>
       <c r="D1337">
-        <v>121.588501</v>
+        <v>121.569569</v>
       </c>
       <c r="E1337">
-        <v>38.924801</v>
+        <v>38.947038</v>
       </c>
     </row>
     <row r="1338" spans="1:5">
@@ -28216,13 +28214,13 @@
         <v>6</v>
       </c>
       <c r="C1338" t="s">
-        <v>91</v>
+        <v>13</v>
       </c>
       <c r="D1338">
-        <v>121.569569</v>
+        <v>108.931192</v>
       </c>
       <c r="E1338">
-        <v>38.947038</v>
+        <v>34.306856</v>
       </c>
     </row>
     <row r="1339" spans="1:5">
@@ -28233,13 +28231,13 @@
         <v>6</v>
       </c>
       <c r="C1339" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="D1339">
-        <v>108.931192</v>
+        <v>105.452272</v>
       </c>
       <c r="E1339">
-        <v>34.306856</v>
+        <v>28.924693</v>
       </c>
     </row>
     <row r="1340" spans="1:5">
@@ -28247,16 +28245,16 @@
         <v>1374</v>
       </c>
       <c r="B1340" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1340" t="s">
-        <v>7</v>
+        <v>347</v>
       </c>
       <c r="D1340">
-        <v>105.452272</v>
+        <v>111.758226</v>
       </c>
       <c r="E1340">
-        <v>28.924693</v>
+        <v>40.820337</v>
       </c>
     </row>
     <row r="1341" spans="1:5">
@@ -28264,16 +28262,16 @@
         <v>1375</v>
       </c>
       <c r="B1341" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1341" t="s">
-        <v>347</v>
+        <v>83</v>
       </c>
       <c r="D1341">
-        <v>111.758226</v>
+        <v>102.763573</v>
       </c>
       <c r="E1341">
-        <v>40.820337</v>
+        <v>24.968333</v>
       </c>
     </row>
     <row r="1342" spans="1:5">
@@ -28284,13 +28282,13 @@
         <v>6</v>
       </c>
       <c r="C1342" t="s">
-        <v>83</v>
+        <v>35</v>
       </c>
       <c r="D1342">
-        <v>102.763573</v>
+        <v>118.125535</v>
       </c>
       <c r="E1342">
-        <v>24.968333</v>
+        <v>24.497394</v>
       </c>
     </row>
     <row r="1343" spans="1:5">
@@ -28298,16 +28296,16 @@
         <v>1377</v>
       </c>
       <c r="B1343" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1343" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="D1343">
-        <v>118.125535</v>
+        <v>114.503824</v>
       </c>
       <c r="E1343">
-        <v>24.497394</v>
+        <v>38.042607</v>
       </c>
     </row>
     <row r="1344" spans="1:5">
@@ -28315,16 +28313,16 @@
         <v>1378</v>
       </c>
       <c r="B1344" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1344" t="s">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="D1344">
-        <v>114.503824</v>
+        <v>120.698696</v>
       </c>
       <c r="E1344">
-        <v>38.042607</v>
+        <v>27.914475</v>
       </c>
     </row>
     <row r="1345" spans="1:5">
@@ -28332,16 +28330,16 @@
         <v>1379</v>
       </c>
       <c r="B1345" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1345" t="s">
-        <v>94</v>
+        <v>347</v>
       </c>
       <c r="D1345">
-        <v>120.698696</v>
+        <v>111.681797</v>
       </c>
       <c r="E1345">
-        <v>27.914475</v>
+        <v>40.778</v>
       </c>
     </row>
     <row r="1346" spans="1:5">
@@ -28352,13 +28350,13 @@
         <v>74</v>
       </c>
       <c r="C1346" t="s">
-        <v>347</v>
+        <v>45</v>
       </c>
       <c r="D1346">
-        <v>111.681797</v>
+        <v>116.432706</v>
       </c>
       <c r="E1346">
-        <v>40.778</v>
+        <v>39.93454</v>
       </c>
     </row>
     <row r="1347" spans="1:5">
@@ -28372,10 +28370,10 @@
         <v>45</v>
       </c>
       <c r="D1347">
-        <v>116.432706</v>
+        <v>116.418073</v>
       </c>
       <c r="E1347">
-        <v>39.93454</v>
+        <v>40.035589</v>
       </c>
     </row>
     <row r="1348" spans="1:5">
@@ -28383,16 +28381,16 @@
         <v>1382</v>
       </c>
       <c r="B1348" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1348" t="s">
-        <v>45</v>
+        <v>94</v>
       </c>
       <c r="D1348">
-        <v>116.418073</v>
+        <v>120.210205</v>
       </c>
       <c r="E1348">
-        <v>40.035589</v>
+        <v>30.343383</v>
       </c>
     </row>
     <row r="1349" spans="1:5">
@@ -28403,13 +28401,13 @@
         <v>6</v>
       </c>
       <c r="C1349" t="s">
-        <v>94</v>
+        <v>20</v>
       </c>
       <c r="D1349">
-        <v>120.210205</v>
+        <v>114.162188</v>
       </c>
       <c r="E1349">
-        <v>30.343383</v>
+        <v>22.737831</v>
       </c>
     </row>
     <row r="1350" spans="1:5">
@@ -28420,13 +28418,13 @@
         <v>6</v>
       </c>
       <c r="C1350" t="s">
-        <v>20</v>
+        <v>207</v>
       </c>
       <c r="D1350">
-        <v>114.162188</v>
+        <v>117.22497</v>
       </c>
       <c r="E1350">
-        <v>22.737831</v>
+        <v>31.783637</v>
       </c>
     </row>
     <row r="1351" spans="1:5">
@@ -28434,16 +28432,16 @@
         <v>1385</v>
       </c>
       <c r="B1351" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1351" t="s">
-        <v>207</v>
+        <v>45</v>
       </c>
       <c r="D1351">
-        <v>117.22497</v>
+        <v>116.330357</v>
       </c>
       <c r="E1351">
-        <v>31.783637</v>
+        <v>39.993931</v>
       </c>
     </row>
     <row r="1352" spans="1:5">
@@ -28451,16 +28449,16 @@
         <v>1386</v>
       </c>
       <c r="B1352" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1352" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="D1352">
-        <v>116.330357</v>
+        <v>104.0707</v>
       </c>
       <c r="E1352">
-        <v>39.993931</v>
+        <v>30.574184</v>
       </c>
     </row>
     <row r="1353" spans="1:5">
@@ -28471,13 +28469,13 @@
         <v>6</v>
       </c>
       <c r="C1353" t="s">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="D1353">
-        <v>104.0707</v>
+        <v>114.371862</v>
       </c>
       <c r="E1353">
-        <v>30.574184</v>
+        <v>30.537579</v>
       </c>
     </row>
     <row r="1354" spans="1:5">
@@ -28485,16 +28483,16 @@
         <v>1388</v>
       </c>
       <c r="B1354" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1354" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D1354">
-        <v>114.371862</v>
+        <v>113.356993</v>
       </c>
       <c r="E1354">
-        <v>30.537579</v>
+        <v>23.10028</v>
       </c>
     </row>
     <row r="1355" spans="1:5">
@@ -28502,16 +28500,16 @@
         <v>1389</v>
       </c>
       <c r="B1355" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1355" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="D1355">
-        <v>113.356993</v>
+        <v>113.801591</v>
       </c>
       <c r="E1355">
-        <v>23.10028</v>
+        <v>34.793487</v>
       </c>
     </row>
     <row r="1356" spans="1:5">
@@ -28525,10 +28523,10 @@
         <v>38</v>
       </c>
       <c r="D1356">
-        <v>113.801591</v>
+        <v>113.556304</v>
       </c>
       <c r="E1356">
-        <v>34.793487</v>
+        <v>34.820019</v>
       </c>
     </row>
     <row r="1357" spans="1:5">
@@ -28539,13 +28537,13 @@
         <v>6</v>
       </c>
       <c r="C1357" t="s">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="D1357">
-        <v>113.556304</v>
+        <v>120.343629</v>
       </c>
       <c r="E1357">
-        <v>34.820019</v>
+        <v>30.317267</v>
       </c>
     </row>
     <row r="1358" spans="1:5">
@@ -28559,10 +28557,10 @@
         <v>94</v>
       </c>
       <c r="D1358">
-        <v>120.343629</v>
+        <v>119.977218</v>
       </c>
       <c r="E1358">
-        <v>30.317267</v>
+        <v>30.360945</v>
       </c>
     </row>
     <row r="1359" spans="1:5">
@@ -28573,13 +28571,13 @@
         <v>6</v>
       </c>
       <c r="C1359" t="s">
-        <v>94</v>
+        <v>154</v>
       </c>
       <c r="D1359">
-        <v>119.977218</v>
+        <v>126.595738</v>
       </c>
       <c r="E1359">
-        <v>30.360945</v>
+        <v>45.792673</v>
       </c>
     </row>
     <row r="1360" spans="1:5">
@@ -28590,13 +28588,13 @@
         <v>6</v>
       </c>
       <c r="C1360" t="s">
-        <v>154</v>
+        <v>207</v>
       </c>
       <c r="D1360">
-        <v>126.595738</v>
+        <v>115.395637</v>
       </c>
       <c r="E1360">
-        <v>45.792673</v>
+        <v>33.250306</v>
       </c>
     </row>
     <row r="1361" spans="1:5">
@@ -28607,13 +28605,13 @@
         <v>6</v>
       </c>
       <c r="C1361" t="s">
-        <v>207</v>
+        <v>7</v>
       </c>
       <c r="D1361">
-        <v>115.395637</v>
+        <v>103.95815</v>
       </c>
       <c r="E1361">
-        <v>33.250306</v>
+        <v>30.673701</v>
       </c>
     </row>
     <row r="1362" spans="1:5">
@@ -28627,10 +28625,10 @@
         <v>7</v>
       </c>
       <c r="D1362">
-        <v>103.95815</v>
+        <v>104.09732</v>
       </c>
       <c r="E1362">
-        <v>30.673701</v>
+        <v>30.71</v>
       </c>
     </row>
     <row r="1363" spans="1:5">
@@ -28641,13 +28639,13 @@
         <v>6</v>
       </c>
       <c r="C1363" t="s">
-        <v>7</v>
+        <v>141</v>
       </c>
       <c r="D1363">
-        <v>104.09732</v>
+        <v>114.463754</v>
       </c>
       <c r="E1363">
-        <v>30.71</v>
+        <v>37.086231</v>
       </c>
     </row>
     <row r="1364" spans="1:5">
@@ -28658,13 +28656,13 @@
         <v>6</v>
       </c>
       <c r="C1364" t="s">
-        <v>141</v>
+        <v>225</v>
       </c>
       <c r="D1364">
-        <v>114.463754</v>
+        <v>110.998812</v>
       </c>
       <c r="E1364">
-        <v>37.086231</v>
+        <v>35.058819</v>
       </c>
     </row>
     <row r="1365" spans="1:5">
@@ -28675,13 +28673,13 @@
         <v>6</v>
       </c>
       <c r="C1365" t="s">
-        <v>225</v>
+        <v>22</v>
       </c>
       <c r="D1365">
-        <v>110.998812</v>
+        <v>114.40241</v>
       </c>
       <c r="E1365">
-        <v>35.058819</v>
+        <v>30.520882</v>
       </c>
     </row>
     <row r="1366" spans="1:5">
@@ -28695,10 +28693,10 @@
         <v>22</v>
       </c>
       <c r="D1366">
-        <v>114.40241</v>
+        <v>114.364825</v>
       </c>
       <c r="E1366">
-        <v>30.520882</v>
+        <v>30.535608</v>
       </c>
     </row>
     <row r="1367" spans="1:5">
@@ -28709,13 +28707,13 @@
         <v>6</v>
       </c>
       <c r="C1367" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D1367">
-        <v>114.364825</v>
+        <v>113.745761</v>
       </c>
       <c r="E1367">
-        <v>30.535608</v>
+        <v>23.028748</v>
       </c>
     </row>
     <row r="1368" spans="1:5">
@@ -28723,16 +28721,16 @@
         <v>1402</v>
       </c>
       <c r="B1368" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1368" t="s">
-        <v>20</v>
+        <v>141</v>
       </c>
       <c r="D1368">
-        <v>113.745761</v>
+        <v>117.960821</v>
       </c>
       <c r="E1368">
-        <v>23.028748</v>
+        <v>40.956596</v>
       </c>
     </row>
     <row r="1369" spans="1:5">
@@ -28740,16 +28738,16 @@
         <v>1403</v>
       </c>
       <c r="B1369" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1369" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="D1369">
-        <v>117.960821</v>
+        <v>117.905405</v>
       </c>
       <c r="E1369">
-        <v>40.956596</v>
+        <v>31.63938</v>
       </c>
     </row>
     <row r="1370" spans="1:5">
@@ -28760,13 +28758,13 @@
         <v>6</v>
       </c>
       <c r="C1370" t="s">
-        <v>207</v>
+        <v>7</v>
       </c>
       <c r="D1370">
-        <v>117.905405</v>
+        <v>103.992618</v>
       </c>
       <c r="E1370">
-        <v>31.63938</v>
+        <v>30.736718</v>
       </c>
     </row>
     <row r="1371" spans="1:5">
@@ -28777,13 +28775,13 @@
         <v>6</v>
       </c>
       <c r="C1371" t="s">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="D1371">
-        <v>103.992618</v>
+        <v>118.423311</v>
       </c>
       <c r="E1371">
-        <v>30.736718</v>
+        <v>24.699202</v>
       </c>
     </row>
     <row r="1372" spans="1:5">
@@ -28797,10 +28795,10 @@
         <v>35</v>
       </c>
       <c r="D1372">
-        <v>118.423311</v>
+        <v>118.399778</v>
       </c>
       <c r="E1372">
-        <v>24.699202</v>
+        <v>24.964816</v>
       </c>
     </row>
     <row r="1373" spans="1:5">
@@ -28814,10 +28812,10 @@
         <v>35</v>
       </c>
       <c r="D1373">
-        <v>118.399778</v>
+        <v>118.250552</v>
       </c>
       <c r="E1373">
-        <v>24.964816</v>
+        <v>25.504823</v>
       </c>
     </row>
     <row r="1374" spans="1:5">
@@ -28828,13 +28826,13 @@
         <v>6</v>
       </c>
       <c r="C1374" t="s">
-        <v>35</v>
+        <v>141</v>
       </c>
       <c r="D1374">
-        <v>118.250552</v>
+        <v>114.428964</v>
       </c>
       <c r="E1374">
-        <v>25.504823</v>
+        <v>38.032442</v>
       </c>
     </row>
     <row r="1375" spans="1:5">
@@ -28848,10 +28846,10 @@
         <v>141</v>
       </c>
       <c r="D1375">
-        <v>114.428964</v>
+        <v>114.532996</v>
       </c>
       <c r="E1375">
-        <v>38.032442</v>
+        <v>38.040332</v>
       </c>
     </row>
     <row r="1376" spans="1:5">
@@ -28859,16 +28857,16 @@
         <v>1410</v>
       </c>
       <c r="B1376" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1376" t="s">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="D1376">
-        <v>114.532996</v>
+        <v>116.307898</v>
       </c>
       <c r="E1376">
-        <v>38.040332</v>
+        <v>39.937566</v>
       </c>
     </row>
     <row r="1377" spans="1:5">
@@ -28876,16 +28874,16 @@
         <v>1411</v>
       </c>
       <c r="B1377" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1377" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="D1377">
-        <v>116.307898</v>
+        <v>119.554583</v>
       </c>
       <c r="E1377">
-        <v>39.937566</v>
+        <v>35.442097</v>
       </c>
     </row>
     <row r="1378" spans="1:5">
@@ -28899,10 +28897,10 @@
         <v>78</v>
       </c>
       <c r="D1378">
-        <v>119.554583</v>
+        <v>120.397581</v>
       </c>
       <c r="E1378">
-        <v>35.442097</v>
+        <v>36.217052</v>
       </c>
     </row>
     <row r="1379" spans="1:5">
@@ -28913,13 +28911,13 @@
         <v>6</v>
       </c>
       <c r="C1379" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="D1379">
-        <v>120.397581</v>
+        <v>122.975658</v>
       </c>
       <c r="E1379">
-        <v>36.217052</v>
+        <v>39.680107</v>
       </c>
     </row>
     <row r="1380" spans="1:5">
@@ -28933,10 +28931,10 @@
         <v>91</v>
       </c>
       <c r="D1380">
-        <v>122.975658</v>
+        <v>121.589282</v>
       </c>
       <c r="E1380">
-        <v>39.680107</v>
+        <v>38.999369</v>
       </c>
     </row>
     <row r="1381" spans="1:5">
@@ -28950,10 +28948,10 @@
         <v>91</v>
       </c>
       <c r="D1381">
-        <v>121.589282</v>
+        <v>121.569902</v>
       </c>
       <c r="E1381">
-        <v>38.999369</v>
+        <v>38.90144</v>
       </c>
     </row>
     <row r="1382" spans="1:5">
@@ -28964,13 +28962,13 @@
         <v>6</v>
       </c>
       <c r="C1382" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="D1382">
-        <v>121.569902</v>
+        <v>102.685808</v>
       </c>
       <c r="E1382">
-        <v>38.90144</v>
+        <v>25.011369</v>
       </c>
     </row>
     <row r="1383" spans="1:5">
@@ -28981,13 +28979,13 @@
         <v>6</v>
       </c>
       <c r="C1383" t="s">
-        <v>83</v>
+        <v>13</v>
       </c>
       <c r="D1383">
-        <v>102.685808</v>
+        <v>108.678065</v>
       </c>
       <c r="E1383">
-        <v>25.011369</v>
+        <v>34.263526</v>
       </c>
     </row>
     <row r="1384" spans="1:5">
@@ -28995,16 +28993,16 @@
         <v>1418</v>
       </c>
       <c r="B1384" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1384" t="s">
-        <v>13</v>
+        <v>45</v>
       </c>
       <c r="D1384">
-        <v>108.678065</v>
+        <v>116.341483</v>
       </c>
       <c r="E1384">
-        <v>34.263526</v>
+        <v>39.726917</v>
       </c>
     </row>
     <row r="1385" spans="1:5">
@@ -29012,16 +29010,16 @@
         <v>1419</v>
       </c>
       <c r="B1385" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1385" t="s">
-        <v>45</v>
+        <v>13</v>
       </c>
       <c r="D1385">
-        <v>116.341483</v>
+        <v>110.455084</v>
       </c>
       <c r="E1385">
-        <v>39.726917</v>
+        <v>35.466599</v>
       </c>
     </row>
     <row r="1386" spans="1:5">
@@ -29035,10 +29033,10 @@
         <v>13</v>
       </c>
       <c r="D1386">
-        <v>110.455084</v>
+        <v>107.253652</v>
       </c>
       <c r="E1386">
-        <v>35.466599</v>
+        <v>34.358048</v>
       </c>
     </row>
     <row r="1387" spans="1:5">
@@ -29049,13 +29047,13 @@
         <v>6</v>
       </c>
       <c r="C1387" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="D1387">
-        <v>107.253652</v>
+        <v>114.337119</v>
       </c>
       <c r="E1387">
-        <v>34.358048</v>
+        <v>30.579281</v>
       </c>
     </row>
     <row r="1388" spans="1:5">
@@ -29069,10 +29067,10 @@
         <v>22</v>
       </c>
       <c r="D1388">
-        <v>114.337119</v>
+        <v>114.344466</v>
       </c>
       <c r="E1388">
-        <v>30.579281</v>
+        <v>30.548272</v>
       </c>
     </row>
     <row r="1389" spans="1:5">
@@ -29086,10 +29084,10 @@
         <v>22</v>
       </c>
       <c r="D1389">
-        <v>114.344466</v>
+        <v>114.346462</v>
       </c>
       <c r="E1389">
-        <v>30.548272</v>
+        <v>30.608005</v>
       </c>
     </row>
     <row r="1390" spans="1:5">
@@ -29103,10 +29101,10 @@
         <v>22</v>
       </c>
       <c r="D1390">
-        <v>114.346462</v>
+        <v>114.320699</v>
       </c>
       <c r="E1390">
-        <v>30.608005</v>
+        <v>30.389928</v>
       </c>
     </row>
     <row r="1391" spans="1:5">
@@ -29120,10 +29118,10 @@
         <v>22</v>
       </c>
       <c r="D1391">
-        <v>114.320699</v>
+        <v>114.321078</v>
       </c>
       <c r="E1391">
-        <v>30.389928</v>
+        <v>30.455839</v>
       </c>
     </row>
     <row r="1392" spans="1:5">
@@ -29134,13 +29132,13 @@
         <v>6</v>
       </c>
       <c r="C1392" t="s">
-        <v>22</v>
+        <v>83</v>
       </c>
       <c r="D1392">
-        <v>114.321078</v>
+        <v>102.746378</v>
       </c>
       <c r="E1392">
-        <v>30.455839</v>
+        <v>25.078695</v>
       </c>
     </row>
     <row r="1393" spans="1:5">
@@ -29151,13 +29149,13 @@
         <v>6</v>
       </c>
       <c r="C1393" t="s">
-        <v>83</v>
+        <v>97</v>
       </c>
       <c r="D1393">
-        <v>102.746378</v>
+        <v>118.666184</v>
       </c>
       <c r="E1393">
-        <v>25.078695</v>
+        <v>32.066489</v>
       </c>
     </row>
     <row r="1394" spans="1:5">
@@ -29168,13 +29166,13 @@
         <v>6</v>
       </c>
       <c r="C1394" t="s">
-        <v>97</v>
+        <v>7</v>
       </c>
       <c r="D1394">
-        <v>118.666184</v>
+        <v>104.67654</v>
       </c>
       <c r="E1394">
-        <v>32.066489</v>
+        <v>28.789745</v>
       </c>
     </row>
     <row r="1395" spans="1:5">
@@ -29188,10 +29186,10 @@
         <v>7</v>
       </c>
       <c r="D1395">
-        <v>104.67654</v>
+        <v>104.981816</v>
       </c>
       <c r="E1395">
-        <v>28.789745</v>
+        <v>28.840532</v>
       </c>
     </row>
     <row r="1396" spans="1:5">
@@ -29205,10 +29203,10 @@
         <v>7</v>
       </c>
       <c r="D1396">
-        <v>104.981816</v>
+        <v>104.966459</v>
       </c>
       <c r="E1396">
-        <v>28.840532</v>
+        <v>28.830298</v>
       </c>
     </row>
     <row r="1397" spans="1:5">
@@ -29222,10 +29220,10 @@
         <v>7</v>
       </c>
       <c r="D1397">
-        <v>104.966459</v>
+        <v>104.107463</v>
       </c>
       <c r="E1397">
-        <v>28.830298</v>
+        <v>30.636161</v>
       </c>
     </row>
     <row r="1398" spans="1:5">
@@ -29236,13 +29234,13 @@
         <v>6</v>
       </c>
       <c r="C1398" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D1398">
-        <v>104.107463</v>
+        <v>108.834399</v>
       </c>
       <c r="E1398">
-        <v>30.636161</v>
+        <v>34.217342</v>
       </c>
     </row>
     <row r="1399" spans="1:5">
@@ -29256,10 +29254,10 @@
         <v>13</v>
       </c>
       <c r="D1399">
-        <v>108.834399</v>
+        <v>109.733876</v>
       </c>
       <c r="E1399">
-        <v>34.217342</v>
+        <v>38.264221</v>
       </c>
     </row>
     <row r="1400" spans="1:5">
@@ -29273,10 +29271,10 @@
         <v>13</v>
       </c>
       <c r="D1400">
-        <v>109.733876</v>
+        <v>109.757174</v>
       </c>
       <c r="E1400">
-        <v>38.264221</v>
+        <v>38.275308</v>
       </c>
     </row>
     <row r="1401" spans="1:5">
@@ -29290,10 +29288,10 @@
         <v>13</v>
       </c>
       <c r="D1401">
-        <v>109.757174</v>
+        <v>109.760438</v>
       </c>
       <c r="E1401">
-        <v>38.275308</v>
+        <v>38.311884</v>
       </c>
     </row>
     <row r="1402" spans="1:5">
@@ -29304,13 +29302,13 @@
         <v>6</v>
       </c>
       <c r="C1402" t="s">
-        <v>13</v>
+        <v>83</v>
       </c>
       <c r="D1402">
-        <v>109.760438</v>
+        <v>102.71289</v>
       </c>
       <c r="E1402">
-        <v>38.311884</v>
+        <v>25.076063</v>
       </c>
     </row>
     <row r="1403" spans="1:5">
@@ -29324,10 +29322,10 @@
         <v>83</v>
       </c>
       <c r="D1403">
-        <v>102.71289</v>
+        <v>102.691312</v>
       </c>
       <c r="E1403">
-        <v>25.076063</v>
+        <v>25.061382</v>
       </c>
     </row>
     <row r="1404" spans="1:5">
@@ -29341,10 +29339,10 @@
         <v>83</v>
       </c>
       <c r="D1404">
-        <v>102.691312</v>
+        <v>102.707654</v>
       </c>
       <c r="E1404">
-        <v>25.061382</v>
+        <v>25.038674</v>
       </c>
     </row>
     <row r="1405" spans="1:5">
@@ -29358,10 +29356,10 @@
         <v>83</v>
       </c>
       <c r="D1405">
-        <v>102.707654</v>
+        <v>102.850052</v>
       </c>
       <c r="E1405">
-        <v>25.038674</v>
+        <v>24.850946</v>
       </c>
     </row>
     <row r="1406" spans="1:5">
@@ -29375,10 +29373,10 @@
         <v>83</v>
       </c>
       <c r="D1406">
-        <v>102.850052</v>
+        <v>102.731221</v>
       </c>
       <c r="E1406">
-        <v>24.850946</v>
+        <v>25.065314</v>
       </c>
     </row>
     <row r="1407" spans="1:5">
@@ -29386,16 +29384,16 @@
         <v>1441</v>
       </c>
       <c r="B1407" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1407" t="s">
-        <v>83</v>
+        <v>7</v>
       </c>
       <c r="D1407">
-        <v>102.731221</v>
+        <v>104.136869</v>
       </c>
       <c r="E1407">
-        <v>25.065314</v>
+        <v>30.476879</v>
       </c>
     </row>
     <row r="1408" spans="1:5">
@@ -29403,16 +29401,16 @@
         <v>1442</v>
       </c>
       <c r="B1408" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1408" t="s">
-        <v>7</v>
+        <v>91</v>
       </c>
       <c r="D1408">
-        <v>104.136869</v>
+        <v>121.653492</v>
       </c>
       <c r="E1408">
-        <v>30.476879</v>
+        <v>38.918416</v>
       </c>
     </row>
     <row r="1409" spans="1:5">
@@ -29426,10 +29424,10 @@
         <v>91</v>
       </c>
       <c r="D1409">
-        <v>121.653492</v>
+        <v>121.682075</v>
       </c>
       <c r="E1409">
-        <v>38.918416</v>
+        <v>38.914547</v>
       </c>
     </row>
     <row r="1410" spans="1:5">
@@ -29443,10 +29441,10 @@
         <v>91</v>
       </c>
       <c r="D1410">
-        <v>121.682075</v>
+        <v>121.644349</v>
       </c>
       <c r="E1410">
-        <v>38.914547</v>
+        <v>38.8853</v>
       </c>
     </row>
     <row r="1411" spans="1:5">
@@ -29460,10 +29458,10 @@
         <v>91</v>
       </c>
       <c r="D1411">
-        <v>121.644349</v>
+        <v>121.676514</v>
       </c>
       <c r="E1411">
-        <v>38.8853</v>
+        <v>38.893422</v>
       </c>
     </row>
     <row r="1412" spans="1:5">
@@ -29471,16 +29469,16 @@
         <v>1446</v>
       </c>
       <c r="B1412" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1412" t="s">
-        <v>91</v>
+        <v>20</v>
       </c>
       <c r="D1412">
-        <v>121.676514</v>
+        <v>113.947629</v>
       </c>
       <c r="E1412">
-        <v>38.893422</v>
+        <v>22.49597</v>
       </c>
     </row>
     <row r="1413" spans="1:5">
@@ -29488,16 +29486,16 @@
         <v>1447</v>
       </c>
       <c r="B1413" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1413" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="D1413">
-        <v>113.947629</v>
+        <v>108.92132</v>
       </c>
       <c r="E1413">
-        <v>22.49597</v>
+        <v>34.27002</v>
       </c>
     </row>
     <row r="1414" spans="1:5">
@@ -29508,13 +29506,13 @@
         <v>6</v>
       </c>
       <c r="C1414" t="s">
-        <v>13</v>
+        <v>207</v>
       </c>
       <c r="D1414">
-        <v>108.92132</v>
+        <v>117.300421</v>
       </c>
       <c r="E1414">
-        <v>34.27002</v>
+        <v>31.839205</v>
       </c>
     </row>
     <row r="1415" spans="1:5">
@@ -29525,13 +29523,13 @@
         <v>6</v>
       </c>
       <c r="C1415" t="s">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c r="D1415">
-        <v>117.300421</v>
+        <v>123.387091</v>
       </c>
       <c r="E1415">
-        <v>31.839205</v>
+        <v>41.737617</v>
       </c>
     </row>
     <row r="1416" spans="1:5">
@@ -29539,16 +29537,16 @@
         <v>1450</v>
       </c>
       <c r="B1416" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1416" t="s">
-        <v>91</v>
+        <v>45</v>
       </c>
       <c r="D1416">
-        <v>123.387091</v>
+        <v>116.379003</v>
       </c>
       <c r="E1416">
-        <v>41.737617</v>
+        <v>39.991594</v>
       </c>
     </row>
     <row r="1417" spans="1:5">
@@ -29556,16 +29554,16 @@
         <v>1451</v>
       </c>
       <c r="B1417" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1417" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="D1417">
-        <v>116.379003</v>
+        <v>118.022959</v>
       </c>
       <c r="E1417">
-        <v>39.991594</v>
+        <v>24.610351</v>
       </c>
     </row>
     <row r="1418" spans="1:5">
@@ -29576,13 +29574,13 @@
         <v>6</v>
       </c>
       <c r="C1418" t="s">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="D1418">
-        <v>118.022959</v>
+        <v>119.128974</v>
       </c>
       <c r="E1418">
-        <v>24.610351</v>
+        <v>36.717775</v>
       </c>
     </row>
     <row r="1419" spans="1:5">
@@ -29593,13 +29591,13 @@
         <v>6</v>
       </c>
       <c r="C1419" t="s">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="D1419">
-        <v>119.128974</v>
+        <v>107.739318</v>
       </c>
       <c r="E1419">
-        <v>36.717775</v>
+        <v>29.873927</v>
       </c>
     </row>
     <row r="1420" spans="1:5">
@@ -29607,16 +29605,16 @@
         <v>1454</v>
       </c>
       <c r="B1420" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1420" t="s">
-        <v>11</v>
+        <v>45</v>
       </c>
       <c r="D1420">
-        <v>107.739318</v>
+        <v>116.437738</v>
       </c>
       <c r="E1420">
-        <v>29.873927</v>
+        <v>39.940881</v>
       </c>
     </row>
     <row r="1421" spans="1:5">
@@ -29624,16 +29622,16 @@
         <v>1455</v>
       </c>
       <c r="B1421" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1421" t="s">
-        <v>45</v>
+        <v>225</v>
       </c>
       <c r="D1421">
-        <v>116.437738</v>
+        <v>111.501603</v>
       </c>
       <c r="E1421">
-        <v>39.940881</v>
+        <v>36.144321</v>
       </c>
     </row>
     <row r="1422" spans="1:5">
@@ -29641,16 +29639,16 @@
         <v>1456</v>
       </c>
       <c r="B1422" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1422" t="s">
-        <v>225</v>
+        <v>45</v>
       </c>
       <c r="D1422">
-        <v>111.501603</v>
+        <v>116.276368</v>
       </c>
       <c r="E1422">
-        <v>36.144321</v>
+        <v>40.034949</v>
       </c>
     </row>
     <row r="1423" spans="1:5">
@@ -29658,16 +29656,16 @@
         <v>1457</v>
       </c>
       <c r="B1423" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1423" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D1423">
-        <v>116.276368</v>
+        <v>112.375081</v>
       </c>
       <c r="E1423">
-        <v>40.034949</v>
+        <v>34.663192</v>
       </c>
     </row>
     <row r="1424" spans="1:5">
@@ -29678,13 +29676,13 @@
         <v>6</v>
       </c>
       <c r="C1424" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="D1424">
-        <v>112.375081</v>
+        <v>117.090984</v>
       </c>
       <c r="E1424">
-        <v>34.663192</v>
+        <v>36.749629</v>
       </c>
     </row>
     <row r="1425" spans="1:5">
@@ -29695,13 +29693,13 @@
         <v>6</v>
       </c>
       <c r="C1425" t="s">
-        <v>78</v>
+        <v>11</v>
       </c>
       <c r="D1425">
-        <v>117.090984</v>
+        <v>106.522981</v>
       </c>
       <c r="E1425">
-        <v>36.749629</v>
+        <v>29.603465</v>
       </c>
     </row>
     <row r="1426" spans="1:5">
@@ -29709,16 +29707,16 @@
         <v>1460</v>
       </c>
       <c r="B1426" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1426" t="s">
-        <v>11</v>
+        <v>78</v>
       </c>
       <c r="D1426">
-        <v>106.522981</v>
+        <v>120.085912</v>
       </c>
       <c r="E1426">
-        <v>29.603465</v>
+        <v>35.892263</v>
       </c>
     </row>
     <row r="1427" spans="1:5">
@@ -29726,16 +29724,16 @@
         <v>1461</v>
       </c>
       <c r="B1427" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1427" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="D1427">
-        <v>120.085912</v>
+        <v>119.967935</v>
       </c>
       <c r="E1427">
-        <v>35.892263</v>
+        <v>31.763229</v>
       </c>
     </row>
     <row r="1428" spans="1:5">
@@ -29746,13 +29744,13 @@
         <v>6</v>
       </c>
       <c r="C1428" t="s">
-        <v>97</v>
+        <v>78</v>
       </c>
       <c r="D1428">
-        <v>119.967935</v>
+        <v>116.897507</v>
       </c>
       <c r="E1428">
-        <v>31.763229</v>
+        <v>36.668019</v>
       </c>
     </row>
     <row r="1429" spans="1:5">
@@ -29763,13 +29761,13 @@
         <v>6</v>
       </c>
       <c r="C1429" t="s">
-        <v>78</v>
+        <v>262</v>
       </c>
       <c r="D1429">
-        <v>116.897507</v>
+        <v>103.752925</v>
       </c>
       <c r="E1429">
-        <v>36.668019</v>
+        <v>36.075519</v>
       </c>
     </row>
     <row r="1430" spans="1:5">
@@ -29780,13 +29778,13 @@
         <v>6</v>
       </c>
       <c r="C1430" t="s">
-        <v>262</v>
+        <v>11</v>
       </c>
       <c r="D1430">
-        <v>103.752925</v>
+        <v>106.275612</v>
       </c>
       <c r="E1430">
-        <v>36.075519</v>
+        <v>29.275586</v>
       </c>
     </row>
     <row r="1431" spans="1:5">
@@ -29797,13 +29795,13 @@
         <v>6</v>
       </c>
       <c r="C1431" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D1431">
-        <v>106.275612</v>
+        <v>104.181073</v>
       </c>
       <c r="E1431">
-        <v>29.275586</v>
+        <v>30.690602</v>
       </c>
     </row>
     <row r="1432" spans="1:5">
@@ -29814,13 +29812,13 @@
         <v>6</v>
       </c>
       <c r="C1432" t="s">
-        <v>7</v>
+        <v>38</v>
       </c>
       <c r="D1432">
-        <v>104.181073</v>
+        <v>113.801361</v>
       </c>
       <c r="E1432">
-        <v>30.690602</v>
+        <v>34.795893</v>
       </c>
     </row>
     <row r="1433" spans="1:5">
@@ -29834,10 +29832,10 @@
         <v>38</v>
       </c>
       <c r="D1433">
-        <v>113.801361</v>
+        <v>113.67179</v>
       </c>
       <c r="E1433">
-        <v>34.795893</v>
+        <v>34.82308</v>
       </c>
     </row>
     <row r="1434" spans="1:5">
@@ -29845,16 +29843,16 @@
         <v>1468</v>
       </c>
       <c r="B1434" t="s">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="C1434" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="D1434">
-        <v>113.67179</v>
+        <v>116.301938</v>
       </c>
       <c r="E1434">
-        <v>34.82308</v>
+        <v>40.054623</v>
       </c>
     </row>
     <row r="1435" spans="1:5">
@@ -29862,16 +29860,16 @@
         <v>1469</v>
       </c>
       <c r="B1435" t="s">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="C1435" t="s">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="D1435">
-        <v>116.301938</v>
+        <v>103.599267</v>
       </c>
       <c r="E1435">
-        <v>40.054623</v>
+        <v>30.894924</v>
       </c>
     </row>
     <row r="1436" spans="1:5">
@@ -29882,13 +29880,13 @@
         <v>6</v>
       </c>
       <c r="C1436" t="s">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="D1436">
-        <v>103.599267</v>
+        <v>116.716209</v>
       </c>
       <c r="E1436">
-        <v>30.894924</v>
+        <v>39.863218</v>
       </c>
     </row>
     <row r="1437" spans="1:5">
@@ -29899,13 +29897,13 @@
         <v>6</v>
       </c>
       <c r="C1437" t="s">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="D1437">
-        <v>116.716209</v>
+        <v>106.563419</v>
       </c>
       <c r="E1437">
-        <v>39.863218</v>
+        <v>29.570345</v>
       </c>
     </row>
     <row r="1438" spans="1:5">
@@ -29916,13 +29914,13 @@
         <v>6</v>
       </c>
       <c r="C1438" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D1438">
-        <v>106.563419</v>
+        <v>104.949552</v>
       </c>
       <c r="E1438">
-        <v>29.570345</v>
+        <v>28.810275</v>
       </c>
     </row>
     <row r="1439" spans="1:5">
@@ -29933,13 +29931,13 @@
         <v>6</v>
       </c>
       <c r="C1439" t="s">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="D1439">
-        <v>104.949552</v>
+        <v>118.3144</v>
       </c>
       <c r="E1439">
-        <v>28.810275</v>
+        <v>35.132723</v>
       </c>
     </row>
     <row r="1440" spans="1:5">
@@ -29953,10 +29951,10 @@
         <v>78</v>
       </c>
       <c r="D1440">
-        <v>118.3144</v>
+        <v>119.155115</v>
       </c>
       <c r="E1440">
-        <v>35.132723</v>
+        <v>36.695759</v>
       </c>
     </row>
     <row r="1441" spans="1:5">
@@ -29970,10 +29968,10 @@
         <v>78</v>
       </c>
       <c r="D1441">
-        <v>119.155115</v>
+        <v>119.19409</v>
       </c>
       <c r="E1441">
-        <v>36.695759</v>
+        <v>36.706602</v>
       </c>
     </row>
     <row r="1442" spans="1:5">
@@ -29987,10 +29985,10 @@
         <v>78</v>
       </c>
       <c r="D1442">
-        <v>119.19409</v>
+        <v>119.178636</v>
       </c>
       <c r="E1442">
-        <v>36.706602</v>
+        <v>36.722727</v>
       </c>
     </row>
     <row r="1443" spans="1:5">
@@ -30004,10 +30002,10 @@
         <v>78</v>
       </c>
       <c r="D1443">
-        <v>119.178636</v>
+        <v>119.187822</v>
       </c>
       <c r="E1443">
-        <v>36.722727</v>
+        <v>36.706473</v>
       </c>
     </row>
     <row r="1444" spans="1:5">
@@ -30021,10 +30019,10 @@
         <v>78</v>
       </c>
       <c r="D1444">
-        <v>119.187822</v>
+        <v>119.188178</v>
       </c>
       <c r="E1444">
-        <v>36.706473</v>
+        <v>36.721025</v>
       </c>
     </row>
     <row r="1445" spans="1:5">
@@ -30038,26 +30036,9 @@
         <v>78</v>
       </c>
       <c r="D1445">
-        <v>119.188178</v>
+        <v>119.187808</v>
       </c>
       <c r="E1445">
-        <v>36.721025</v>
-      </c>
-    </row>
-    <row r="1446" spans="1:5">
-      <c r="A1446" t="s">
-        <v>1480</v>
-      </c>
-      <c r="B1446" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1446" t="s">
-        <v>78</v>
-      </c>
-      <c r="D1446">
-        <v>119.187808</v>
-      </c>
-      <c r="E1446">
         <v>36.711359</v>
       </c>
     </row>
